--- a/WinterGame2026_コスト表.xlsx
+++ b/WinterGame2026_コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kudosyota\Desktop\GitHub\WinterGame2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skoto\AppData\Local\Temp\claude\C--Users-skoto--claude-spares-spare-M0pqxg\03067e3a-b310-4656-b145-965eea2f8c0f\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F13EC36-C3A7-4753-8E49-61FB0E1523D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F41C55A-C425-44D0-A149-2EB4FA6A9FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2670" yWindow="600" windowWidth="24120" windowHeight="14880" activeTab="2" xr2:uid="{8B56E59A-6A48-4E9E-98F0-BB372CB837AE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8B56E59A-6A48-4E9E-98F0-BB372CB837AE}"/>
   </bookViews>
   <sheets>
     <sheet name="集計" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="241">
   <si>
     <t>WinterGame2026 設定</t>
   </si>
@@ -790,6 +790,14 @@
   </si>
   <si>
     <t>進捗率 = 状態が「完了」のタスクの見積コスト ÷ 見積コスト合計。見積と実績の差 = 完了タスクの実コスト − その見積コスト（プラス = 見積より多くかかった）。</t>
+  </si>
+  <si>
+    <t>完了</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>進行中</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -1840,7 +1848,7 @@
       </c>
       <c r="C4" s="7">
         <f>COUNTIFS(タスク一覧!$E$2:$E$116,$A4,タスク一覧!$G$2:$G$116,"完了")</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D4" s="7">
         <f>SUMPRODUCT((タスク一覧!$E$2:$E$116=$A4)*(タスク一覧!$H$2:$H$116=0))</f>
@@ -1877,7 +1885,7 @@
       </c>
       <c r="C5" s="7">
         <f>COUNTIFS(タスク一覧!$E$2:$E$116,$A5,タスク一覧!$G$2:$G$116,"完了")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" s="7">
         <f>SUMPRODUCT((タスク一覧!$E$2:$E$116=$A5)*(タスク一覧!$H$2:$H$116=0))</f>
@@ -1914,7 +1922,7 @@
       </c>
       <c r="C6" s="7">
         <f>COUNTIFS(タスク一覧!$E$2:$E$116,$A6,タスク一覧!$G$2:$G$116,"完了")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="7">
         <f>SUMPRODUCT((タスク一覧!$E$2:$E$116=$A6)*(タスク一覧!$H$2:$H$116=0))</f>
@@ -1988,7 +1996,7 @@
       </c>
       <c r="C8" s="96">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="D8" s="96">
         <f t="shared" si="0"/>
@@ -2696,7 +2704,7 @@
         <v>20</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
@@ -2720,7 +2728,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="H3" s="32"/>
       <c r="I3" s="32"/>
@@ -2744,7 +2752,7 @@
         <v>20</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
@@ -2816,7 +2824,7 @@
         <v>20</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
@@ -2864,7 +2872,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
@@ -2888,7 +2896,7 @@
         <v>20</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
@@ -2912,7 +2920,7 @@
         <v>20</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
@@ -2984,7 +2992,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="H14" s="32"/>
       <c r="I14" s="32"/>
@@ -3008,7 +3016,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
@@ -3032,7 +3040,7 @@
         <v>20</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
@@ -3056,7 +3064,7 @@
         <v>20</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="H17" s="32"/>
       <c r="I17" s="32"/>
@@ -3104,7 +3112,7 @@
         <v>20</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H19" s="32"/>
       <c r="I19" s="32"/>
@@ -3128,7 +3136,7 @@
         <v>20</v>
       </c>
       <c r="G20" s="36" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H20" s="37"/>
       <c r="I20" s="37"/>
@@ -3152,7 +3160,7 @@
         <v>20</v>
       </c>
       <c r="G21" s="36" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H21" s="37"/>
       <c r="I21" s="37"/>
@@ -3176,7 +3184,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="36" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H22" s="37"/>
       <c r="I22" s="37"/>
@@ -3200,7 +3208,7 @@
         <v>20</v>
       </c>
       <c r="G23" s="36" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H23" s="37"/>
       <c r="I23" s="37"/>
@@ -3224,7 +3232,7 @@
         <v>20</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H24" s="37"/>
       <c r="I24" s="37"/>
@@ -3248,7 +3256,7 @@
         <v>20</v>
       </c>
       <c r="G25" s="36" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H25" s="37"/>
       <c r="I25" s="37"/>
@@ -3272,7 +3280,7 @@
         <v>20</v>
       </c>
       <c r="G26" s="36" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H26" s="37"/>
       <c r="I26" s="37"/>
@@ -3296,7 +3304,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="36" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H27" s="37"/>
       <c r="I27" s="37"/>
@@ -3320,7 +3328,7 @@
         <v>20</v>
       </c>
       <c r="G28" s="36" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H28" s="37"/>
       <c r="I28" s="37"/>
@@ -3368,7 +3376,7 @@
         <v>20</v>
       </c>
       <c r="G30" s="36" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H30" s="37"/>
       <c r="I30" s="37"/>
@@ -3392,7 +3400,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="36" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H31" s="37"/>
       <c r="I31" s="37"/>
@@ -3416,7 +3424,7 @@
         <v>20</v>
       </c>
       <c r="G32" s="36" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H32" s="37"/>
       <c r="I32" s="37"/>
@@ -3440,7 +3448,7 @@
         <v>20</v>
       </c>
       <c r="G33" s="41" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H33" s="42"/>
       <c r="I33" s="42"/>
@@ -3464,7 +3472,7 @@
         <v>20</v>
       </c>
       <c r="G34" s="41" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="H34" s="42"/>
       <c r="I34" s="42"/>
@@ -3488,7 +3496,7 @@
         <v>20</v>
       </c>
       <c r="G35" s="41" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H35" s="42"/>
       <c r="I35" s="42"/>
@@ -3514,7 +3522,7 @@
         <v>20</v>
       </c>
       <c r="G36" s="41" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H36" s="42"/>
       <c r="I36" s="42"/>
@@ -3538,7 +3546,7 @@
         <v>20</v>
       </c>
       <c r="G37" s="46" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="H37" s="47"/>
       <c r="I37" s="47"/>
@@ -3564,7 +3572,7 @@
         <v>20</v>
       </c>
       <c r="G38" s="46" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="H38" s="47"/>
       <c r="I38" s="47"/>
@@ -3588,7 +3596,7 @@
         <v>20</v>
       </c>
       <c r="G39" s="46" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="H39" s="47"/>
       <c r="I39" s="47"/>
@@ -3612,7 +3620,7 @@
         <v>20</v>
       </c>
       <c r="G40" s="51" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H40" s="52"/>
       <c r="I40" s="52"/>
@@ -3636,7 +3644,7 @@
         <v>20</v>
       </c>
       <c r="G41" s="51" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H41" s="52"/>
       <c r="I41" s="52"/>
@@ -3660,7 +3668,7 @@
         <v>20</v>
       </c>
       <c r="G42" s="51" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H42" s="52"/>
       <c r="I42" s="52"/>
@@ -3684,7 +3692,7 @@
         <v>20</v>
       </c>
       <c r="G43" s="51" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H43" s="52"/>
       <c r="I43" s="52"/>
@@ -3708,7 +3716,7 @@
         <v>20</v>
       </c>
       <c r="G44" s="51" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H44" s="52"/>
       <c r="I44" s="52"/>
@@ -3732,7 +3740,7 @@
         <v>20</v>
       </c>
       <c r="G45" s="51" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="H45" s="52"/>
       <c r="I45" s="52"/>
@@ -3756,7 +3764,7 @@
         <v>20</v>
       </c>
       <c r="G46" s="56" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H46" s="57"/>
       <c r="I46" s="57"/>
@@ -3780,7 +3788,7 @@
         <v>20</v>
       </c>
       <c r="G47" s="56" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H47" s="57"/>
       <c r="I47" s="57"/>
@@ -3978,7 +3986,7 @@
         <v>20</v>
       </c>
       <c r="G55" s="61" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H55" s="62"/>
       <c r="I55" s="62"/>
@@ -4026,7 +4034,7 @@
         <v>20</v>
       </c>
       <c r="G57" s="61" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H57" s="62"/>
       <c r="I57" s="62"/>
@@ -4050,7 +4058,7 @@
         <v>20</v>
       </c>
       <c r="G58" s="61" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H58" s="62"/>
       <c r="I58" s="62"/>
@@ -4098,7 +4106,7 @@
         <v>20</v>
       </c>
       <c r="G60" s="61" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="H60" s="62"/>
       <c r="I60" s="62"/>
@@ -4522,7 +4530,7 @@
         <v>20</v>
       </c>
       <c r="G77" s="66" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H77" s="67"/>
       <c r="I77" s="67"/>
@@ -4546,7 +4554,7 @@
         <v>20</v>
       </c>
       <c r="G78" s="66" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="H78" s="67"/>
       <c r="I78" s="67"/>
@@ -4570,7 +4578,7 @@
         <v>20</v>
       </c>
       <c r="G79" s="66" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="H79" s="67"/>
       <c r="I79" s="67"/>
@@ -4594,7 +4602,7 @@
         <v>20</v>
       </c>
       <c r="G80" s="66" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="H80" s="67"/>
       <c r="I80" s="67"/>
@@ -4644,7 +4652,7 @@
         <v>20</v>
       </c>
       <c r="G82" s="71" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H82" s="72"/>
       <c r="I82" s="72"/>
@@ -4668,7 +4676,7 @@
         <v>20</v>
       </c>
       <c r="G83" s="71" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H83" s="72"/>
       <c r="I83" s="72"/>
@@ -5352,7 +5360,7 @@
         <v>20</v>
       </c>
       <c r="G111" s="86" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="H111" s="87"/>
       <c r="I111" s="87"/>

--- a/WinterGame2026_コスト表.xlsx
+++ b/WinterGame2026_コスト表.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skoto\AppData\Local\Temp\claude\C--Users-skoto--claude-spares-spare-M0pqxg\03067e3a-b310-4656-b145-965eea2f8c0f\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skoto\Git\WinterGame2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F41C55A-C425-44D0-A149-2EB4FA6A9FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EDF4FC-5A22-454B-B927-28852F9410BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8B56E59A-6A48-4E9E-98F0-BB372CB837AE}"/>
+    <workbookView xWindow="8385" yWindow="0" windowWidth="16095" windowHeight="10170" activeTab="2" xr2:uid="{8B56E59A-6A48-4E9E-98F0-BB372CB837AE}"/>
   </bookViews>
   <sheets>
     <sheet name="集計" sheetId="1" r:id="rId1"/>
     <sheet name="カレンダー" sheetId="4" r:id="rId2"/>
     <sheet name="タスク一覧" sheetId="2" r:id="rId3"/>
     <sheet name="設定" sheetId="3" r:id="rId4"/>
+    <sheet name="memo" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">タスク一覧!$A$1:$J$116</definedName>
@@ -70,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="245">
   <si>
     <t>WinterGame2026 設定</t>
   </si>
@@ -797,6 +798,46 @@
   </si>
   <si>
     <t>進行中</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>デカイ手の演出終わらせる</t>
+    <rPh sb="3" eb="4">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>エイリアンの挙動も完成させる</t>
+    <rPh sb="6" eb="8">
+      <t>キョドウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>竜巻を豪鬼の大竜にする</t>
+    <rPh sb="0" eb="2">
+      <t>タツマキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゴウキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ダイリュウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>∞</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1852,11 +1893,11 @@
       </c>
       <c r="D4" s="7">
         <f>SUMPRODUCT((タスク一覧!$E$2:$E$116=$A4)*(タスク一覧!$H$2:$H$116=0))</f>
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="E4" s="97">
         <f>SUMIF(タスク一覧!$E$2:$E$116,$A4,タスク一覧!$H$2:$H$116)</f>
-        <v>0</v>
+        <v>146.5</v>
       </c>
       <c r="F4" s="97">
         <f>SUMIF(タスク一覧!$E$2:$E$116,$A4,タスク一覧!$I$2:$I$116)</f>
@@ -1864,15 +1905,15 @@
       </c>
       <c r="G4" s="97">
         <f>SUMIFS(タスク一覧!$H$2:$H$116,タスク一覧!$E$2:$E$116,$A4,タスク一覧!$G$2:$G$116,"完了")</f>
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="H4" s="12">
         <f>IFERROR(G4/E4,0)</f>
-        <v>0</v>
+        <v>0.50170648464163825</v>
       </c>
       <c r="I4" s="99">
         <f>SUMIFS(タスク一覧!$I$2:$I$116,タスク一覧!$E$2:$E$116,$A4,タスク一覧!$G$2:$G$116,"完了")-G4</f>
-        <v>0</v>
+        <v>-73.5</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1889,11 +1930,11 @@
       </c>
       <c r="D5" s="7">
         <f>SUMPRODUCT((タスク一覧!$E$2:$E$116=$A5)*(タスク一覧!$H$2:$H$116=0))</f>
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E5" s="97">
         <f>SUMIF(タスク一覧!$E$2:$E$116,$A5,タスク一覧!$H$2:$H$116)</f>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F5" s="97">
         <f>SUMIF(タスク一覧!$E$2:$E$116,$A5,タスク一覧!$I$2:$I$116)</f>
@@ -1901,15 +1942,15 @@
       </c>
       <c r="G5" s="97">
         <f>SUMIFS(タスク一覧!$H$2:$H$116,タスク一覧!$E$2:$E$116,$A5,タスク一覧!$G$2:$G$116,"完了")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" s="12">
         <f>IFERROR(G5/E5,0)</f>
-        <v>0</v>
+        <v>3.3898305084745763E-2</v>
       </c>
       <c r="I5" s="99">
         <f>SUMIFS(タスク一覧!$I$2:$I$116,タスク一覧!$E$2:$E$116,$A5,タスク一覧!$G$2:$G$116,"完了")-G5</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1926,11 +1967,11 @@
       </c>
       <c r="D6" s="7">
         <f>SUMPRODUCT((タスク一覧!$E$2:$E$116=$A6)*(タスク一覧!$H$2:$H$116=0))</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E6" s="97">
         <f>SUMIF(タスク一覧!$E$2:$E$116,$A6,タスク一覧!$H$2:$H$116)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F6" s="97">
         <f>SUMIF(タスク一覧!$E$2:$E$116,$A6,タスク一覧!$I$2:$I$116)</f>
@@ -1938,15 +1979,15 @@
       </c>
       <c r="G6" s="97">
         <f>SUMIFS(タスク一覧!$H$2:$H$116,タスク一覧!$E$2:$E$116,$A6,タスク一覧!$G$2:$G$116,"完了")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="12">
         <f>IFERROR(G6/E6,0)</f>
-        <v>0</v>
+        <v>3.125E-2</v>
       </c>
       <c r="I6" s="99">
         <f>SUMIFS(タスク一覧!$I$2:$I$116,タスク一覧!$E$2:$E$116,$A6,タスク一覧!$G$2:$G$116,"完了")-G6</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1963,11 +2004,11 @@
       </c>
       <c r="D7" s="7">
         <f>SUMPRODUCT((タスク一覧!$E$2:$E$116=$A7)*(タスク一覧!$H$2:$H$116=0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="97">
         <f>SUMIF(タスク一覧!$E$2:$E$116,$A7,タスク一覧!$H$2:$H$116)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="97">
         <f>SUMIF(タスク一覧!$E$2:$E$116,$A7,タスク一覧!$I$2:$I$116)</f>
@@ -2000,11 +2041,11 @@
       </c>
       <c r="D8" s="96">
         <f t="shared" si="0"/>
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="E8" s="98">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>238.5</v>
       </c>
       <c r="F8" s="98">
         <f t="shared" si="0"/>
@@ -2012,15 +2053,15 @@
       </c>
       <c r="G8" s="98">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="H8" s="14">
         <f>IFERROR(G8/E8,0)</f>
-        <v>0</v>
+        <v>0.32075471698113206</v>
       </c>
       <c r="I8" s="100">
         <f>SUM(I4:I7)</f>
-        <v>0</v>
+        <v>-76.5</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2095,11 +2136,11 @@
       </c>
       <c r="F4" s="18">
         <f>SUMIF(タスク一覧!$E:$E,A4,タスク一覧!$H:$H)*設定!$B$5</f>
-        <v>0</v>
+        <v>146.5</v>
       </c>
       <c r="G4" s="18">
         <f>E4-F4</f>
-        <v>248</v>
+        <v>101.5</v>
       </c>
       <c r="I4" s="22" t="s">
         <v>60</v>
@@ -2125,11 +2166,11 @@
       </c>
       <c r="F5" s="18">
         <f>SUMIF(タスク一覧!$E:$E,A5,タスク一覧!$H:$H)*設定!$B$5</f>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G5" s="18">
         <f>E5-F5</f>
-        <v>240</v>
+        <v>181</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>61</v>
@@ -2155,11 +2196,11 @@
       </c>
       <c r="F6" s="18">
         <f>SUMIF(タスク一覧!$E:$E,A6,タスク一覧!$H:$H)*設定!$B$5</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G6" s="18">
         <f>E6-F6</f>
-        <v>184</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -2182,11 +2223,11 @@
       </c>
       <c r="F7" s="18">
         <f>SUMIF(タスク一覧!$E:$E,A7,タスク一覧!$H:$H)*設定!$B$5</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="18">
         <f>E7-F7</f>
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="16.5">
@@ -2706,7 +2747,9 @@
       <c r="G2" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="H2" s="32"/>
+      <c r="H2" s="32">
+        <v>0.5</v>
+      </c>
       <c r="I2" s="32"/>
       <c r="J2" s="33"/>
     </row>
@@ -2730,7 +2773,9 @@
       <c r="G3" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="H3" s="32"/>
+      <c r="H3" s="32">
+        <v>3</v>
+      </c>
       <c r="I3" s="32"/>
       <c r="J3" s="33"/>
     </row>
@@ -2754,7 +2799,9 @@
       <c r="G4" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="H4" s="32"/>
+      <c r="H4" s="32">
+        <v>0.5</v>
+      </c>
       <c r="I4" s="32"/>
       <c r="J4" s="33"/>
     </row>
@@ -2778,7 +2825,9 @@
       <c r="G5" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="32"/>
+      <c r="H5" s="32">
+        <v>0.5</v>
+      </c>
       <c r="I5" s="32"/>
       <c r="J5" s="33"/>
     </row>
@@ -2802,7 +2851,9 @@
       <c r="G6" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="32"/>
+      <c r="H6" s="32">
+        <v>0.5</v>
+      </c>
       <c r="I6" s="32"/>
       <c r="J6" s="33"/>
     </row>
@@ -2826,7 +2877,9 @@
       <c r="G7" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="H7" s="32"/>
+      <c r="H7" s="32">
+        <v>0.5</v>
+      </c>
       <c r="I7" s="32"/>
       <c r="J7" s="33"/>
     </row>
@@ -2850,7 +2903,9 @@
       <c r="G8" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="32"/>
+      <c r="H8" s="32">
+        <v>0.5</v>
+      </c>
       <c r="I8" s="32"/>
       <c r="J8" s="33"/>
     </row>
@@ -2874,7 +2929,9 @@
       <c r="G9" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="H9" s="32"/>
+      <c r="H9" s="32">
+        <v>0.5</v>
+      </c>
       <c r="I9" s="32"/>
       <c r="J9" s="33"/>
     </row>
@@ -2898,7 +2955,9 @@
       <c r="G10" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="H10" s="32"/>
+      <c r="H10" s="32">
+        <v>0.5</v>
+      </c>
       <c r="I10" s="32"/>
       <c r="J10" s="33"/>
     </row>
@@ -2922,7 +2981,9 @@
       <c r="G11" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="H11" s="32"/>
+      <c r="H11" s="32">
+        <v>0.5</v>
+      </c>
       <c r="I11" s="32"/>
       <c r="J11" s="33"/>
     </row>
@@ -2946,7 +3007,9 @@
       <c r="G12" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="32"/>
+      <c r="H12" s="32">
+        <v>5</v>
+      </c>
       <c r="I12" s="32"/>
       <c r="J12" s="33"/>
     </row>
@@ -2970,7 +3033,9 @@
       <c r="G13" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="32">
+        <v>0.5</v>
+      </c>
       <c r="I13" s="32"/>
       <c r="J13" s="33"/>
     </row>
@@ -2994,7 +3059,9 @@
       <c r="G14" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="H14" s="32"/>
+      <c r="H14" s="32">
+        <v>0.5</v>
+      </c>
       <c r="I14" s="32"/>
       <c r="J14" s="33"/>
     </row>
@@ -3018,7 +3085,9 @@
       <c r="G15" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="H15" s="32"/>
+      <c r="H15" s="32">
+        <v>0.5</v>
+      </c>
       <c r="I15" s="32"/>
       <c r="J15" s="33"/>
     </row>
@@ -3042,7 +3111,9 @@
       <c r="G16" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="H16" s="32"/>
+      <c r="H16" s="32">
+        <v>0.5</v>
+      </c>
       <c r="I16" s="32"/>
       <c r="J16" s="33"/>
     </row>
@@ -3066,7 +3137,9 @@
       <c r="G17" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="H17" s="32"/>
+      <c r="H17" s="32">
+        <v>3</v>
+      </c>
       <c r="I17" s="32"/>
       <c r="J17" s="33"/>
     </row>
@@ -3090,7 +3163,9 @@
       <c r="G18" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="32"/>
+      <c r="H18" s="32">
+        <v>4</v>
+      </c>
       <c r="I18" s="32"/>
       <c r="J18" s="33"/>
     </row>
@@ -3114,7 +3189,9 @@
       <c r="G19" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="H19" s="32"/>
+      <c r="H19" s="32">
+        <v>7</v>
+      </c>
       <c r="I19" s="32"/>
       <c r="J19" s="33"/>
     </row>
@@ -3138,7 +3215,9 @@
       <c r="G20" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="H20" s="37"/>
+      <c r="H20" s="37">
+        <v>5</v>
+      </c>
       <c r="I20" s="37"/>
       <c r="J20" s="38"/>
     </row>
@@ -3162,7 +3241,9 @@
       <c r="G21" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="H21" s="37"/>
+      <c r="H21" s="37">
+        <v>5</v>
+      </c>
       <c r="I21" s="37"/>
       <c r="J21" s="38"/>
     </row>
@@ -3186,7 +3267,9 @@
       <c r="G22" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="H22" s="37"/>
+      <c r="H22" s="37">
+        <v>3</v>
+      </c>
       <c r="I22" s="37"/>
       <c r="J22" s="38"/>
     </row>
@@ -3210,7 +3293,9 @@
       <c r="G23" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="H23" s="37"/>
+      <c r="H23" s="37">
+        <v>2</v>
+      </c>
       <c r="I23" s="37"/>
       <c r="J23" s="38"/>
     </row>
@@ -3234,7 +3319,9 @@
       <c r="G24" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="H24" s="37"/>
+      <c r="H24" s="37">
+        <v>3</v>
+      </c>
       <c r="I24" s="37"/>
       <c r="J24" s="38"/>
     </row>
@@ -3258,7 +3345,9 @@
       <c r="G25" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="H25" s="37"/>
+      <c r="H25" s="37">
+        <v>3</v>
+      </c>
       <c r="I25" s="37"/>
       <c r="J25" s="38"/>
     </row>
@@ -3282,7 +3371,9 @@
       <c r="G26" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="H26" s="37"/>
+      <c r="H26" s="37">
+        <v>3</v>
+      </c>
       <c r="I26" s="37"/>
       <c r="J26" s="38"/>
     </row>
@@ -3306,7 +3397,9 @@
       <c r="G27" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="H27" s="37"/>
+      <c r="H27" s="37">
+        <v>3</v>
+      </c>
       <c r="I27" s="37"/>
       <c r="J27" s="38"/>
     </row>
@@ -3330,7 +3423,9 @@
       <c r="G28" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="H28" s="37"/>
+      <c r="H28" s="37">
+        <v>3</v>
+      </c>
       <c r="I28" s="37"/>
       <c r="J28" s="38"/>
     </row>
@@ -3354,7 +3449,9 @@
       <c r="G29" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="37"/>
+      <c r="H29" s="37">
+        <v>4</v>
+      </c>
       <c r="I29" s="37"/>
       <c r="J29" s="38"/>
     </row>
@@ -3378,7 +3475,9 @@
       <c r="G30" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="H30" s="37"/>
+      <c r="H30" s="37">
+        <v>2</v>
+      </c>
       <c r="I30" s="37"/>
       <c r="J30" s="38"/>
     </row>
@@ -3402,7 +3501,9 @@
       <c r="G31" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="H31" s="37"/>
+      <c r="H31" s="37">
+        <v>4</v>
+      </c>
       <c r="I31" s="37"/>
       <c r="J31" s="38"/>
     </row>
@@ -3426,7 +3527,9 @@
       <c r="G32" s="36" t="s">
         <v>239</v>
       </c>
-      <c r="H32" s="37"/>
+      <c r="H32" s="37">
+        <v>4</v>
+      </c>
       <c r="I32" s="37"/>
       <c r="J32" s="38"/>
     </row>
@@ -3450,7 +3553,9 @@
       <c r="G33" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="H33" s="42"/>
+      <c r="H33" s="42">
+        <v>2</v>
+      </c>
       <c r="I33" s="42"/>
       <c r="J33" s="43"/>
     </row>
@@ -3474,7 +3579,9 @@
       <c r="G34" s="41" t="s">
         <v>240</v>
       </c>
-      <c r="H34" s="42"/>
+      <c r="H34" s="42">
+        <v>4</v>
+      </c>
       <c r="I34" s="42"/>
       <c r="J34" s="43"/>
     </row>
@@ -3498,7 +3605,9 @@
       <c r="G35" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="H35" s="42"/>
+      <c r="H35" s="42">
+        <v>3</v>
+      </c>
       <c r="I35" s="42"/>
       <c r="J35" s="43" t="s">
         <v>230</v>
@@ -3524,7 +3633,9 @@
       <c r="G36" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="H36" s="42"/>
+      <c r="H36" s="42">
+        <v>2</v>
+      </c>
       <c r="I36" s="42"/>
       <c r="J36" s="43"/>
     </row>
@@ -3548,7 +3659,9 @@
       <c r="G37" s="46" t="s">
         <v>240</v>
       </c>
-      <c r="H37" s="47"/>
+      <c r="H37" s="47">
+        <v>3</v>
+      </c>
       <c r="I37" s="47"/>
       <c r="J37" s="48" t="s">
         <v>118</v>
@@ -3574,7 +3687,9 @@
       <c r="G38" s="46" t="s">
         <v>240</v>
       </c>
-      <c r="H38" s="47"/>
+      <c r="H38" s="47">
+        <v>3</v>
+      </c>
       <c r="I38" s="47"/>
       <c r="J38" s="48"/>
     </row>
@@ -3598,7 +3713,9 @@
       <c r="G39" s="46" t="s">
         <v>240</v>
       </c>
-      <c r="H39" s="47"/>
+      <c r="H39" s="47">
+        <v>3</v>
+      </c>
       <c r="I39" s="47"/>
       <c r="J39" s="48"/>
     </row>
@@ -3622,7 +3739,9 @@
       <c r="G40" s="51" t="s">
         <v>239</v>
       </c>
-      <c r="H40" s="52"/>
+      <c r="H40" s="52">
+        <v>2</v>
+      </c>
       <c r="I40" s="52"/>
       <c r="J40" s="53"/>
     </row>
@@ -3646,7 +3765,9 @@
       <c r="G41" s="51" t="s">
         <v>239</v>
       </c>
-      <c r="H41" s="52"/>
+      <c r="H41" s="52">
+        <v>2</v>
+      </c>
       <c r="I41" s="52"/>
       <c r="J41" s="53"/>
     </row>
@@ -3670,7 +3791,9 @@
       <c r="G42" s="51" t="s">
         <v>239</v>
       </c>
-      <c r="H42" s="52"/>
+      <c r="H42" s="52">
+        <v>2</v>
+      </c>
       <c r="I42" s="52"/>
       <c r="J42" s="53"/>
     </row>
@@ -3694,7 +3817,9 @@
       <c r="G43" s="51" t="s">
         <v>239</v>
       </c>
-      <c r="H43" s="52"/>
+      <c r="H43" s="52">
+        <v>2</v>
+      </c>
       <c r="I43" s="52"/>
       <c r="J43" s="53"/>
     </row>
@@ -3718,7 +3843,9 @@
       <c r="G44" s="51" t="s">
         <v>239</v>
       </c>
-      <c r="H44" s="52"/>
+      <c r="H44" s="52">
+        <v>2</v>
+      </c>
       <c r="I44" s="52"/>
       <c r="J44" s="53"/>
     </row>
@@ -3742,7 +3869,9 @@
       <c r="G45" s="51" t="s">
         <v>240</v>
       </c>
-      <c r="H45" s="52"/>
+      <c r="H45" s="52">
+        <v>3</v>
+      </c>
       <c r="I45" s="52"/>
       <c r="J45" s="53"/>
     </row>
@@ -3766,7 +3895,9 @@
       <c r="G46" s="56" t="s">
         <v>239</v>
       </c>
-      <c r="H46" s="57"/>
+      <c r="H46" s="57">
+        <v>0.5</v>
+      </c>
       <c r="I46" s="57"/>
       <c r="J46" s="58"/>
     </row>
@@ -3790,7 +3921,9 @@
       <c r="G47" s="56" t="s">
         <v>239</v>
       </c>
-      <c r="H47" s="57"/>
+      <c r="H47" s="57">
+        <v>0.5</v>
+      </c>
       <c r="I47" s="57"/>
       <c r="J47" s="58"/>
     </row>
@@ -3814,7 +3947,9 @@
       <c r="G48" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="H48" s="57"/>
+      <c r="H48" s="57">
+        <v>3</v>
+      </c>
       <c r="I48" s="57"/>
       <c r="J48" s="58"/>
     </row>
@@ -3838,7 +3973,9 @@
       <c r="G49" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="H49" s="57"/>
+      <c r="H49" s="57">
+        <v>2</v>
+      </c>
       <c r="I49" s="57"/>
       <c r="J49" s="58"/>
     </row>
@@ -3862,7 +3999,9 @@
       <c r="G50" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="H50" s="57"/>
+      <c r="H50" s="57">
+        <v>3</v>
+      </c>
       <c r="I50" s="57"/>
       <c r="J50" s="58" t="s">
         <v>136</v>
@@ -3888,7 +4027,9 @@
       <c r="G51" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H51" s="62"/>
+      <c r="H51" s="62">
+        <v>5</v>
+      </c>
       <c r="I51" s="62"/>
       <c r="J51" s="63"/>
     </row>
@@ -3912,7 +4053,9 @@
       <c r="G52" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H52" s="62"/>
+      <c r="H52" s="62">
+        <v>5</v>
+      </c>
       <c r="I52" s="62"/>
       <c r="J52" s="63"/>
     </row>
@@ -3936,7 +4079,9 @@
       <c r="G53" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H53" s="62"/>
+      <c r="H53" s="62">
+        <v>2</v>
+      </c>
       <c r="I53" s="62"/>
       <c r="J53" s="63" t="s">
         <v>141</v>
@@ -3962,7 +4107,9 @@
       <c r="G54" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H54" s="62"/>
+      <c r="H54" s="62">
+        <v>1</v>
+      </c>
       <c r="I54" s="62"/>
       <c r="J54" s="63" t="s">
         <v>143</v>
@@ -3988,7 +4135,9 @@
       <c r="G55" s="61" t="s">
         <v>239</v>
       </c>
-      <c r="H55" s="62"/>
+      <c r="H55" s="62">
+        <v>3</v>
+      </c>
       <c r="I55" s="62"/>
       <c r="J55" s="63"/>
     </row>
@@ -4012,7 +4161,9 @@
       <c r="G56" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H56" s="62"/>
+      <c r="H56" s="62">
+        <v>2</v>
+      </c>
       <c r="I56" s="62"/>
       <c r="J56" s="63"/>
     </row>
@@ -4036,7 +4187,9 @@
       <c r="G57" s="61" t="s">
         <v>239</v>
       </c>
-      <c r="H57" s="62"/>
+      <c r="H57" s="62">
+        <v>0.5</v>
+      </c>
       <c r="I57" s="62"/>
       <c r="J57" s="63"/>
     </row>
@@ -4060,7 +4213,9 @@
       <c r="G58" s="61" t="s">
         <v>239</v>
       </c>
-      <c r="H58" s="62"/>
+      <c r="H58" s="62">
+        <v>0.5</v>
+      </c>
       <c r="I58" s="62"/>
       <c r="J58" s="63"/>
     </row>
@@ -4084,7 +4239,9 @@
       <c r="G59" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H59" s="62"/>
+      <c r="H59" s="62">
+        <v>2</v>
+      </c>
       <c r="I59" s="62"/>
       <c r="J59" s="63"/>
     </row>
@@ -4108,7 +4265,9 @@
       <c r="G60" s="61" t="s">
         <v>240</v>
       </c>
-      <c r="H60" s="62"/>
+      <c r="H60" s="62">
+        <v>3</v>
+      </c>
       <c r="I60" s="62"/>
       <c r="J60" s="63"/>
     </row>
@@ -4132,7 +4291,9 @@
       <c r="G61" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H61" s="62"/>
+      <c r="H61" s="62">
+        <v>2</v>
+      </c>
       <c r="I61" s="62"/>
       <c r="J61" s="63"/>
     </row>
@@ -4156,7 +4317,9 @@
       <c r="G62" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H62" s="62"/>
+      <c r="H62" s="62">
+        <v>3</v>
+      </c>
       <c r="I62" s="62"/>
       <c r="J62" s="63"/>
     </row>
@@ -4180,7 +4343,9 @@
       <c r="G63" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H63" s="62"/>
+      <c r="H63" s="62">
+        <v>3</v>
+      </c>
       <c r="I63" s="62"/>
       <c r="J63" s="63" t="s">
         <v>154</v>
@@ -4206,7 +4371,9 @@
       <c r="G64" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H64" s="62"/>
+      <c r="H64" s="62">
+        <v>2</v>
+      </c>
       <c r="I64" s="62"/>
       <c r="J64" s="63"/>
     </row>
@@ -4230,7 +4397,9 @@
       <c r="G65" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H65" s="62"/>
+      <c r="H65" s="62">
+        <v>2</v>
+      </c>
       <c r="I65" s="62"/>
       <c r="J65" s="63" t="s">
         <v>157</v>
@@ -4256,7 +4425,9 @@
       <c r="G66" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H66" s="62"/>
+      <c r="H66" s="62">
+        <v>2</v>
+      </c>
       <c r="I66" s="62"/>
       <c r="J66" s="63"/>
     </row>
@@ -4280,7 +4451,9 @@
       <c r="G67" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H67" s="62"/>
+      <c r="H67" s="62">
+        <v>2</v>
+      </c>
       <c r="I67" s="62"/>
       <c r="J67" s="63"/>
     </row>
@@ -4304,7 +4477,9 @@
       <c r="G68" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H68" s="62"/>
+      <c r="H68" s="62">
+        <v>2</v>
+      </c>
       <c r="I68" s="62"/>
       <c r="J68" s="63" t="s">
         <v>160</v>
@@ -4330,7 +4505,9 @@
       <c r="G69" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H69" s="62"/>
+      <c r="H69" s="62">
+        <v>2</v>
+      </c>
       <c r="I69" s="62"/>
       <c r="J69" s="63" t="s">
         <v>162</v>
@@ -4356,7 +4533,9 @@
       <c r="G70" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H70" s="62"/>
+      <c r="H70" s="62">
+        <v>2</v>
+      </c>
       <c r="I70" s="62"/>
       <c r="J70" s="63" t="s">
         <v>164</v>
@@ -4382,7 +4561,9 @@
       <c r="G71" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H71" s="62"/>
+      <c r="H71" s="62">
+        <v>2</v>
+      </c>
       <c r="I71" s="62"/>
       <c r="J71" s="63" t="s">
         <v>166</v>
@@ -4408,7 +4589,9 @@
       <c r="G72" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H72" s="62"/>
+      <c r="H72" s="62">
+        <v>2</v>
+      </c>
       <c r="I72" s="62"/>
       <c r="J72" s="63" t="s">
         <v>168</v>
@@ -4434,7 +4617,9 @@
       <c r="G73" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H73" s="62"/>
+      <c r="H73" s="62">
+        <v>2</v>
+      </c>
       <c r="I73" s="62"/>
       <c r="J73" s="63" t="s">
         <v>170</v>
@@ -4460,7 +4645,9 @@
       <c r="G74" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H74" s="62"/>
+      <c r="H74" s="62">
+        <v>2</v>
+      </c>
       <c r="I74" s="62"/>
       <c r="J74" s="63"/>
     </row>
@@ -4484,7 +4671,9 @@
       <c r="G75" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H75" s="62"/>
+      <c r="H75" s="62">
+        <v>2</v>
+      </c>
       <c r="I75" s="62"/>
       <c r="J75" s="63"/>
     </row>
@@ -4508,7 +4697,9 @@
       <c r="G76" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="H76" s="62"/>
+      <c r="H76" s="62">
+        <v>2</v>
+      </c>
       <c r="I76" s="62"/>
       <c r="J76" s="63"/>
     </row>
@@ -4532,7 +4723,9 @@
       <c r="G77" s="66" t="s">
         <v>239</v>
       </c>
-      <c r="H77" s="67"/>
+      <c r="H77" s="67">
+        <v>1</v>
+      </c>
       <c r="I77" s="67"/>
       <c r="J77" s="68"/>
     </row>
@@ -4556,7 +4749,9 @@
       <c r="G78" s="66" t="s">
         <v>240</v>
       </c>
-      <c r="H78" s="67"/>
+      <c r="H78" s="67">
+        <v>1</v>
+      </c>
       <c r="I78" s="67"/>
       <c r="J78" s="68"/>
     </row>
@@ -4580,7 +4775,9 @@
       <c r="G79" s="66" t="s">
         <v>240</v>
       </c>
-      <c r="H79" s="67"/>
+      <c r="H79" s="67">
+        <v>1</v>
+      </c>
       <c r="I79" s="67"/>
       <c r="J79" s="68"/>
     </row>
@@ -4604,7 +4801,9 @@
       <c r="G80" s="66" t="s">
         <v>240</v>
       </c>
-      <c r="H80" s="67"/>
+      <c r="H80" s="67">
+        <v>1</v>
+      </c>
       <c r="I80" s="67"/>
       <c r="J80" s="68" t="s">
         <v>183</v>
@@ -4630,7 +4829,9 @@
       <c r="G81" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="H81" s="67"/>
+      <c r="H81" s="67">
+        <v>1</v>
+      </c>
       <c r="I81" s="67"/>
       <c r="J81" s="68"/>
     </row>
@@ -4654,7 +4855,9 @@
       <c r="G82" s="71" t="s">
         <v>239</v>
       </c>
-      <c r="H82" s="72"/>
+      <c r="H82" s="72">
+        <v>1</v>
+      </c>
       <c r="I82" s="72"/>
       <c r="J82" s="73"/>
     </row>
@@ -4678,7 +4881,9 @@
       <c r="G83" s="71" t="s">
         <v>239</v>
       </c>
-      <c r="H83" s="72"/>
+      <c r="H83" s="72">
+        <v>1</v>
+      </c>
       <c r="I83" s="72"/>
       <c r="J83" s="73"/>
     </row>
@@ -4702,7 +4907,9 @@
       <c r="G84" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="H84" s="72"/>
+      <c r="H84" s="72">
+        <v>2</v>
+      </c>
       <c r="I84" s="72"/>
       <c r="J84" s="73"/>
     </row>
@@ -4726,7 +4933,9 @@
       <c r="G85" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="H85" s="72"/>
+      <c r="H85" s="72">
+        <v>3</v>
+      </c>
       <c r="I85" s="72"/>
       <c r="J85" s="73"/>
     </row>
@@ -4750,7 +4959,9 @@
       <c r="G86" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H86" s="77"/>
+      <c r="H86" s="77">
+        <v>3</v>
+      </c>
       <c r="I86" s="77"/>
       <c r="J86" s="78"/>
     </row>
@@ -4774,7 +4985,9 @@
       <c r="G87" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H87" s="77"/>
+      <c r="H87" s="77">
+        <v>3</v>
+      </c>
       <c r="I87" s="77"/>
       <c r="J87" s="78" t="s">
         <v>193</v>
@@ -4800,7 +5013,9 @@
       <c r="G88" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H88" s="77"/>
+      <c r="H88" s="77">
+        <v>1</v>
+      </c>
       <c r="I88" s="77"/>
       <c r="J88" s="78"/>
     </row>
@@ -4824,7 +5039,9 @@
       <c r="G89" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H89" s="77"/>
+      <c r="H89" s="77">
+        <v>3</v>
+      </c>
       <c r="I89" s="77"/>
       <c r="J89" s="78"/>
     </row>
@@ -4848,7 +5065,9 @@
       <c r="G90" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H90" s="77"/>
+      <c r="H90" s="77">
+        <v>2</v>
+      </c>
       <c r="I90" s="77"/>
       <c r="J90" s="78"/>
     </row>
@@ -4872,7 +5091,9 @@
       <c r="G91" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H91" s="77"/>
+      <c r="H91" s="77">
+        <v>2</v>
+      </c>
       <c r="I91" s="77"/>
       <c r="J91" s="78"/>
     </row>
@@ -4896,7 +5117,9 @@
       <c r="G92" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H92" s="77"/>
+      <c r="H92" s="77">
+        <v>2</v>
+      </c>
       <c r="I92" s="77"/>
       <c r="J92" s="78" t="s">
         <v>198</v>
@@ -4922,7 +5145,9 @@
       <c r="G93" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H93" s="77"/>
+      <c r="H93" s="77">
+        <v>2</v>
+      </c>
       <c r="I93" s="77"/>
       <c r="J93" s="78"/>
     </row>
@@ -4946,7 +5171,9 @@
       <c r="G94" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H94" s="77"/>
+      <c r="H94" s="77">
+        <v>2</v>
+      </c>
       <c r="I94" s="77"/>
       <c r="J94" s="78"/>
     </row>
@@ -4970,7 +5197,9 @@
       <c r="G95" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H95" s="77"/>
+      <c r="H95" s="77">
+        <v>1</v>
+      </c>
       <c r="I95" s="77"/>
       <c r="J95" s="78"/>
     </row>
@@ -4994,7 +5223,9 @@
       <c r="G96" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="H96" s="82"/>
+      <c r="H96" s="82">
+        <v>3</v>
+      </c>
       <c r="I96" s="82"/>
       <c r="J96" s="83"/>
     </row>
@@ -5018,7 +5249,9 @@
       <c r="G97" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="H97" s="82"/>
+      <c r="H97" s="82">
+        <v>3</v>
+      </c>
       <c r="I97" s="82"/>
       <c r="J97" s="83"/>
     </row>
@@ -5042,7 +5275,9 @@
       <c r="G98" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="H98" s="82"/>
+      <c r="H98" s="82">
+        <v>2</v>
+      </c>
       <c r="I98" s="82"/>
       <c r="J98" s="83"/>
     </row>
@@ -5066,7 +5301,9 @@
       <c r="G99" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="H99" s="82"/>
+      <c r="H99" s="82">
+        <v>3</v>
+      </c>
       <c r="I99" s="82"/>
       <c r="J99" s="83" t="s">
         <v>207</v>
@@ -5092,7 +5329,9 @@
       <c r="G100" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="H100" s="82"/>
+      <c r="H100" s="82">
+        <v>4</v>
+      </c>
       <c r="I100" s="82"/>
       <c r="J100" s="83" t="s">
         <v>209</v>
@@ -5118,7 +5357,9 @@
       <c r="G101" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="H101" s="82"/>
+      <c r="H101" s="82">
+        <v>3</v>
+      </c>
       <c r="I101" s="82"/>
       <c r="J101" s="83" t="s">
         <v>210</v>
@@ -5144,7 +5385,9 @@
       <c r="G102" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="H102" s="82"/>
+      <c r="H102" s="82">
+        <v>4</v>
+      </c>
       <c r="I102" s="82"/>
       <c r="J102" s="83" t="s">
         <v>212</v>
@@ -5170,7 +5413,9 @@
       <c r="G103" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="H103" s="87"/>
+      <c r="H103" s="87">
+        <v>1</v>
+      </c>
       <c r="I103" s="87"/>
       <c r="J103" s="88"/>
     </row>
@@ -5194,7 +5439,9 @@
       <c r="G104" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="H104" s="87"/>
+      <c r="H104" s="87">
+        <v>1</v>
+      </c>
       <c r="I104" s="87"/>
       <c r="J104" s="88"/>
     </row>
@@ -5218,7 +5465,9 @@
       <c r="G105" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="H105" s="87"/>
+      <c r="H105" s="87">
+        <v>1</v>
+      </c>
       <c r="I105" s="87"/>
       <c r="J105" s="88"/>
     </row>
@@ -5242,7 +5491,9 @@
       <c r="G106" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="H106" s="87"/>
+      <c r="H106" s="87">
+        <v>1</v>
+      </c>
       <c r="I106" s="87"/>
       <c r="J106" s="88"/>
     </row>
@@ -5266,7 +5517,9 @@
       <c r="G107" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="H107" s="87"/>
+      <c r="H107" s="87">
+        <v>1</v>
+      </c>
       <c r="I107" s="87"/>
       <c r="J107" s="88"/>
     </row>
@@ -5290,7 +5543,9 @@
       <c r="G108" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="H108" s="87"/>
+      <c r="H108" s="87">
+        <v>1</v>
+      </c>
       <c r="I108" s="87"/>
       <c r="J108" s="88"/>
     </row>
@@ -5314,7 +5569,9 @@
       <c r="G109" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="H109" s="87"/>
+      <c r="H109" s="87">
+        <v>1</v>
+      </c>
       <c r="I109" s="87"/>
       <c r="J109" s="88"/>
     </row>
@@ -5338,7 +5595,9 @@
       <c r="G110" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="H110" s="87"/>
+      <c r="H110" s="87">
+        <v>1</v>
+      </c>
       <c r="I110" s="87"/>
       <c r="J110" s="88"/>
     </row>
@@ -5362,7 +5621,9 @@
       <c r="G111" s="86" t="s">
         <v>239</v>
       </c>
-      <c r="H111" s="87"/>
+      <c r="H111" s="87">
+        <v>1</v>
+      </c>
       <c r="I111" s="87"/>
       <c r="J111" s="88"/>
     </row>
@@ -5386,7 +5647,9 @@
       <c r="G112" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="H112" s="87"/>
+      <c r="H112" s="87">
+        <v>1</v>
+      </c>
       <c r="I112" s="87"/>
       <c r="J112" s="88"/>
     </row>
@@ -5410,7 +5673,9 @@
       <c r="G113" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="H113" s="92"/>
+      <c r="H113" s="87" t="s">
+        <v>244</v>
+      </c>
       <c r="I113" s="92"/>
       <c r="J113" s="93" t="s">
         <v>225</v>
@@ -5436,7 +5701,9 @@
       <c r="G114" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="H114" s="92"/>
+      <c r="H114" s="87" t="s">
+        <v>244</v>
+      </c>
       <c r="I114" s="92"/>
       <c r="J114" s="93"/>
     </row>
@@ -5460,7 +5727,9 @@
       <c r="G115" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="H115" s="92"/>
+      <c r="H115" s="87" t="s">
+        <v>244</v>
+      </c>
       <c r="I115" s="92"/>
       <c r="J115" s="93"/>
     </row>
@@ -5484,7 +5753,9 @@
       <c r="G116" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="H116" s="92"/>
+      <c r="H116" s="87">
+        <v>1</v>
+      </c>
       <c r="I116" s="92"/>
       <c r="J116" s="93"/>
     </row>
@@ -5500,7 +5771,7 @@
       <c r="G117" s="94"/>
       <c r="H117" s="95">
         <f>SUM(H2:H116)</f>
-        <v>0</v>
+        <v>238.5</v>
       </c>
       <c r="I117" s="95">
         <f>SUM(I2:I116)</f>
@@ -5606,4 +5877,35 @@
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1D838DA-6C01-4DFD-980E-9C45A10CBCD9}">
+  <dimension ref="A2:B5"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="B3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="B4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="B5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/WinterGame2026_コスト表.xlsx
+++ b/WinterGame2026_コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skoto\Git\WinterGame2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kudosyota\Desktop\GitHub\WinterGame2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EDF4FC-5A22-454B-B927-28852F9410BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD58E1F-2FAF-43D9-9E52-3354C4FBC3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8385" yWindow="0" windowWidth="16095" windowHeight="10170" activeTab="2" xr2:uid="{8B56E59A-6A48-4E9E-98F0-BB372CB837AE}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8B56E59A-6A48-4E9E-98F0-BB372CB837AE}"/>
   </bookViews>
   <sheets>
     <sheet name="集計" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="memo" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">タスク一覧!$A$1:$J$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">タスク一覧!$A$1:$J$117</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="249">
   <si>
     <t>WinterGame2026 設定</t>
   </si>
@@ -460,9 +460,6 @@
     <t>弾</t>
   </si>
   <si>
-    <t>弾とキャラ・弾と地形</t>
-  </si>
-  <si>
     <t>通常</t>
   </si>
   <si>
@@ -481,16 +478,10 @@
     <t>一時的なカメラ切り替え</t>
   </si>
   <si>
-    <t>ボス登場・とどめなど</t>
-  </si>
-  <si>
     <t>共通</t>
   </si>
   <si>
     <t>被弾・怯み</t>
-  </si>
-  <si>
-    <t>吹っ飛び・打ち上げ・ダウン・起き上がり</t>
   </si>
   <si>
     <t>死亡ステート・消え方</t>
@@ -837,8 +828,59 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>∞</t>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>弾とキャラ・弾と地形</t>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ボス登場・とどめなど</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>吹っ飛び・打ち上げ・ダウン・起き上がり</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>タイムスケールとか重力を考えると吹っ飛び難しい(打ち上げの空中感はアルファでやる)</t>
+    <rPh sb="9" eb="11">
+      <t>ジュウリョク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ムズカ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>完了</t>
+  </si>
+  <si>
+    <t>進行中</t>
   </si>
 </sst>
 </file>
@@ -1858,25 +1900,25 @@
         <v>44</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>45</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F3" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>236</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>47</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1885,11 +1927,11 @@
       </c>
       <c r="B4" s="7">
         <f>COUNTIF(タスク一覧!$E$2:$E$116,$A4)</f>
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C4" s="7">
         <f>COUNTIFS(タスク一覧!$E$2:$E$116,$A4,タスク一覧!$G$2:$G$116,"完了")</f>
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D4" s="7">
         <f>SUMPRODUCT((タスク一覧!$E$2:$E$116=$A4)*(タスク一覧!$H$2:$H$116=0))</f>
@@ -1897,7 +1939,7 @@
       </c>
       <c r="E4" s="97">
         <f>SUMIF(タスク一覧!$E$2:$E$116,$A4,タスク一覧!$H$2:$H$116)</f>
-        <v>146.5</v>
+        <v>144.5</v>
       </c>
       <c r="F4" s="97">
         <f>SUMIF(タスク一覧!$E$2:$E$116,$A4,タスク一覧!$I$2:$I$116)</f>
@@ -1905,15 +1947,15 @@
       </c>
       <c r="G4" s="97">
         <f>SUMIFS(タスク一覧!$H$2:$H$116,タスク一覧!$E$2:$E$116,$A4,タスク一覧!$G$2:$G$116,"完了")</f>
-        <v>73.5</v>
+        <v>77.5</v>
       </c>
       <c r="H4" s="12">
         <f>IFERROR(G4/E4,0)</f>
-        <v>0.50170648464163825</v>
+        <v>0.53633217993079585</v>
       </c>
       <c r="I4" s="99">
         <f>SUMIFS(タスク一覧!$I$2:$I$116,タスク一覧!$E$2:$E$116,$A4,タスク一覧!$G$2:$G$116,"完了")-G4</f>
-        <v>-73.5</v>
+        <v>-77.5</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1922,7 +1964,7 @@
       </c>
       <c r="B5" s="7">
         <f>COUNTIF(タスク一覧!$E$2:$E$116,$A5)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" s="7">
         <f>COUNTIFS(タスク一覧!$E$2:$E$116,$A5,タスク一覧!$G$2:$G$116,"完了")</f>
@@ -1934,7 +1976,7 @@
       </c>
       <c r="E5" s="97">
         <f>SUMIF(タスク一覧!$E$2:$E$116,$A5,タスク一覧!$H$2:$H$116)</f>
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F5" s="97">
         <f>SUMIF(タスク一覧!$E$2:$E$116,$A5,タスク一覧!$I$2:$I$116)</f>
@@ -1946,7 +1988,7 @@
       </c>
       <c r="H5" s="12">
         <f>IFERROR(G5/E5,0)</f>
-        <v>3.3898305084745763E-2</v>
+        <v>3.125E-2</v>
       </c>
       <c r="I5" s="99">
         <f>SUMIFS(タスク一覧!$I$2:$I$116,タスク一覧!$E$2:$E$116,$A5,タスク一覧!$G$2:$G$116,"完了")-G5</f>
@@ -1971,7 +2013,7 @@
       </c>
       <c r="E6" s="97">
         <f>SUMIF(タスク一覧!$E$2:$E$116,$A6,タスク一覧!$H$2:$H$116)</f>
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="F6" s="97">
         <f>SUMIF(タスク一覧!$E$2:$E$116,$A6,タスク一覧!$I$2:$I$116)</f>
@@ -1983,7 +2025,7 @@
       </c>
       <c r="H6" s="12">
         <f>IFERROR(G6/E6,0)</f>
-        <v>3.125E-2</v>
+        <v>1.6129032258064516E-2</v>
       </c>
       <c r="I6" s="99">
         <f>SUMIFS(タスク一覧!$I$2:$I$116,タスク一覧!$E$2:$E$116,$A6,タスク一覧!$G$2:$G$116,"完了")-G6</f>
@@ -2037,7 +2079,7 @@
       </c>
       <c r="C8" s="96">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D8" s="96">
         <f t="shared" si="0"/>
@@ -2045,7 +2087,7 @@
       </c>
       <c r="E8" s="98">
         <f t="shared" si="0"/>
-        <v>238.5</v>
+        <v>271.5</v>
       </c>
       <c r="F8" s="98">
         <f t="shared" si="0"/>
@@ -2053,20 +2095,20 @@
       </c>
       <c r="G8" s="98">
         <f t="shared" si="0"/>
-        <v>76.5</v>
+        <v>80.5</v>
       </c>
       <c r="H8" s="14">
         <f>IFERROR(G8/E8,0)</f>
-        <v>0.32075471698113206</v>
+        <v>0.2965009208103131</v>
       </c>
       <c r="I8" s="100">
         <f>SUM(I4:I7)</f>
-        <v>-76.5</v>
+        <v>-80.5</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2136,11 +2178,11 @@
       </c>
       <c r="F4" s="18">
         <f>SUMIF(タスク一覧!$E:$E,A4,タスク一覧!$H:$H)*設定!$B$5</f>
-        <v>146.5</v>
+        <v>144.5</v>
       </c>
       <c r="G4" s="18">
         <f>E4-F4</f>
-        <v>101.5</v>
+        <v>103.5</v>
       </c>
       <c r="I4" s="22" t="s">
         <v>60</v>
@@ -2166,11 +2208,11 @@
       </c>
       <c r="F5" s="18">
         <f>SUMIF(タスク一覧!$E:$E,A5,タスク一覧!$H:$H)*設定!$B$5</f>
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G5" s="18">
         <f>E5-F5</f>
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>61</v>
@@ -2196,11 +2238,11 @@
       </c>
       <c r="F6" s="18">
         <f>SUMIF(タスク一覧!$E:$E,A6,タスク一覧!$H:$H)*設定!$B$5</f>
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="G6" s="18">
         <f>E6-F6</f>
-        <v>152</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -2681,6 +2723,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F591B56F-9C16-43FE-9B5C-FD4AC86E6A15}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J117"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -2718,16 +2761,16 @@
         <v>14</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="J1" s="28" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" hidden="1">
       <c r="A2" s="29" t="s">
         <v>17</v>
       </c>
@@ -2745,7 +2788,7 @@
         <v>20</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H2" s="32">
         <v>0.5</v>
@@ -2771,7 +2814,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H3" s="32">
         <v>3</v>
@@ -2779,7 +2822,7 @@
       <c r="I3" s="32"/>
       <c r="J3" s="33"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" hidden="1">
       <c r="A4" s="29" t="s">
         <v>17</v>
       </c>
@@ -2797,7 +2840,7 @@
         <v>20</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H4" s="32">
         <v>0.5</v>
@@ -2846,7 +2889,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="G6" s="31" t="s">
         <v>21</v>
@@ -2857,7 +2900,7 @@
       <c r="I6" s="32"/>
       <c r="J6" s="33"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" hidden="1">
       <c r="A7" s="29" t="s">
         <v>17</v>
       </c>
@@ -2875,7 +2918,7 @@
         <v>20</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H7" s="32">
         <v>0.5</v>
@@ -2927,7 +2970,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H9" s="32">
         <v>0.5</v>
@@ -2935,7 +2978,7 @@
       <c r="I9" s="32"/>
       <c r="J9" s="33"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" hidden="1">
       <c r="A10" s="29" t="s">
         <v>17</v>
       </c>
@@ -2953,7 +2996,7 @@
         <v>20</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H10" s="32">
         <v>0.5</v>
@@ -2961,7 +3004,7 @@
       <c r="I10" s="32"/>
       <c r="J10" s="33"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" hidden="1">
       <c r="A11" s="29" t="s">
         <v>17</v>
       </c>
@@ -2979,7 +3022,7 @@
         <v>20</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H11" s="32">
         <v>0.5</v>
@@ -3057,7 +3100,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H14" s="32">
         <v>0.5</v>
@@ -3065,7 +3108,7 @@
       <c r="I14" s="32"/>
       <c r="J14" s="33"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" hidden="1">
       <c r="A15" s="29" t="s">
         <v>17</v>
       </c>
@@ -3083,7 +3126,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H15" s="32">
         <v>0.5</v>
@@ -3091,7 +3134,7 @@
       <c r="I15" s="32"/>
       <c r="J15" s="33"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" hidden="1">
       <c r="A16" s="29" t="s">
         <v>17</v>
       </c>
@@ -3109,7 +3152,7 @@
         <v>20</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H16" s="32">
         <v>0.5</v>
@@ -3135,10 +3178,10 @@
         <v>20</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H17" s="32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17" s="32"/>
       <c r="J17" s="33"/>
@@ -3158,7 +3201,7 @@
         <v>19</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>20</v>
+        <v>242</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>21</v>
@@ -3169,7 +3212,7 @@
       <c r="I18" s="32"/>
       <c r="J18" s="33"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" hidden="1">
       <c r="A19" s="29" t="s">
         <v>17</v>
       </c>
@@ -3187,7 +3230,7 @@
         <v>20</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H19" s="32">
         <v>7</v>
@@ -3195,7 +3238,7 @@
       <c r="I19" s="32"/>
       <c r="J19" s="33"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" hidden="1">
       <c r="A20" s="34" t="s">
         <v>24</v>
       </c>
@@ -3213,7 +3256,7 @@
         <v>20</v>
       </c>
       <c r="G20" s="36" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H20" s="37">
         <v>5</v>
@@ -3221,7 +3264,7 @@
       <c r="I20" s="37"/>
       <c r="J20" s="38"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" hidden="1">
       <c r="A21" s="34" t="s">
         <v>24</v>
       </c>
@@ -3239,7 +3282,7 @@
         <v>20</v>
       </c>
       <c r="G21" s="36" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H21" s="37">
         <v>5</v>
@@ -3247,7 +3290,7 @@
       <c r="I21" s="37"/>
       <c r="J21" s="38"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" hidden="1">
       <c r="A22" s="34" t="s">
         <v>24</v>
       </c>
@@ -3265,7 +3308,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="36" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H22" s="37">
         <v>3</v>
@@ -3273,7 +3316,7 @@
       <c r="I22" s="37"/>
       <c r="J22" s="38"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" hidden="1">
       <c r="A23" s="34" t="s">
         <v>24</v>
       </c>
@@ -3291,7 +3334,7 @@
         <v>20</v>
       </c>
       <c r="G23" s="36" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H23" s="37">
         <v>2</v>
@@ -3299,7 +3342,7 @@
       <c r="I23" s="37"/>
       <c r="J23" s="38"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" hidden="1">
       <c r="A24" s="34" t="s">
         <v>24</v>
       </c>
@@ -3317,7 +3360,7 @@
         <v>20</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H24" s="37">
         <v>3</v>
@@ -3325,7 +3368,7 @@
       <c r="I24" s="37"/>
       <c r="J24" s="38"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" hidden="1">
       <c r="A25" s="34" t="s">
         <v>24</v>
       </c>
@@ -3343,7 +3386,7 @@
         <v>20</v>
       </c>
       <c r="G25" s="36" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H25" s="37">
         <v>3</v>
@@ -3351,7 +3394,7 @@
       <c r="I25" s="37"/>
       <c r="J25" s="38"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" hidden="1">
       <c r="A26" s="34" t="s">
         <v>24</v>
       </c>
@@ -3369,7 +3412,7 @@
         <v>20</v>
       </c>
       <c r="G26" s="36" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H26" s="37">
         <v>3</v>
@@ -3377,7 +3420,7 @@
       <c r="I26" s="37"/>
       <c r="J26" s="38"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" hidden="1">
       <c r="A27" s="34" t="s">
         <v>24</v>
       </c>
@@ -3395,7 +3438,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="36" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H27" s="37">
         <v>3</v>
@@ -3403,7 +3446,7 @@
       <c r="I27" s="37"/>
       <c r="J27" s="38"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" hidden="1">
       <c r="A28" s="34" t="s">
         <v>24</v>
       </c>
@@ -3421,7 +3464,7 @@
         <v>20</v>
       </c>
       <c r="G28" s="36" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H28" s="37">
         <v>3</v>
@@ -3455,7 +3498,7 @@
       <c r="I29" s="37"/>
       <c r="J29" s="38"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" hidden="1">
       <c r="A30" s="34" t="s">
         <v>24</v>
       </c>
@@ -3473,7 +3516,7 @@
         <v>20</v>
       </c>
       <c r="G30" s="36" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H30" s="37">
         <v>2</v>
@@ -3481,7 +3524,7 @@
       <c r="I30" s="37"/>
       <c r="J30" s="38"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" hidden="1">
       <c r="A31" s="34" t="s">
         <v>24</v>
       </c>
@@ -3499,7 +3542,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="36" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H31" s="37">
         <v>4</v>
@@ -3507,7 +3550,7 @@
       <c r="I31" s="37"/>
       <c r="J31" s="38"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" hidden="1">
       <c r="A32" s="34" t="s">
         <v>24</v>
       </c>
@@ -3525,7 +3568,7 @@
         <v>20</v>
       </c>
       <c r="G32" s="36" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H32" s="37">
         <v>4</v>
@@ -3533,7 +3576,7 @@
       <c r="I32" s="37"/>
       <c r="J32" s="38"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" hidden="1">
       <c r="A33" s="39" t="s">
         <v>23</v>
       </c>
@@ -3551,7 +3594,7 @@
         <v>20</v>
       </c>
       <c r="G33" s="41" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H33" s="42">
         <v>2</v>
@@ -3577,7 +3620,7 @@
         <v>20</v>
       </c>
       <c r="G34" s="41" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H34" s="42">
         <v>4</v>
@@ -3585,7 +3628,7 @@
       <c r="I34" s="42"/>
       <c r="J34" s="43"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" hidden="1">
       <c r="A35" s="39" t="s">
         <v>23</v>
       </c>
@@ -3603,17 +3646,17 @@
         <v>20</v>
       </c>
       <c r="G35" s="41" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H35" s="42">
         <v>3</v>
       </c>
       <c r="I35" s="42"/>
       <c r="J35" s="43" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" hidden="1">
       <c r="A36" s="39" t="s">
         <v>23</v>
       </c>
@@ -3631,7 +3674,7 @@
         <v>20</v>
       </c>
       <c r="G36" s="41" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H36" s="42">
         <v>2</v>
@@ -3657,7 +3700,7 @@
         <v>20</v>
       </c>
       <c r="G37" s="46" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H37" s="47">
         <v>3</v>
@@ -3685,7 +3728,7 @@
         <v>20</v>
       </c>
       <c r="G38" s="46" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H38" s="47">
         <v>3</v>
@@ -3711,7 +3754,7 @@
         <v>20</v>
       </c>
       <c r="G39" s="46" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H39" s="47">
         <v>3</v>
@@ -3719,7 +3762,7 @@
       <c r="I39" s="47"/>
       <c r="J39" s="48"/>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" hidden="1">
       <c r="A40" s="49" t="s">
         <v>52</v>
       </c>
@@ -3737,7 +3780,7 @@
         <v>20</v>
       </c>
       <c r="G40" s="51" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H40" s="52">
         <v>2</v>
@@ -3745,7 +3788,7 @@
       <c r="I40" s="52"/>
       <c r="J40" s="53"/>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" hidden="1">
       <c r="A41" s="49" t="s">
         <v>52</v>
       </c>
@@ -3763,7 +3806,7 @@
         <v>20</v>
       </c>
       <c r="G41" s="51" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H41" s="52">
         <v>2</v>
@@ -3771,7 +3814,7 @@
       <c r="I41" s="52"/>
       <c r="J41" s="53"/>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" hidden="1">
       <c r="A42" s="49" t="s">
         <v>52</v>
       </c>
@@ -3789,7 +3832,7 @@
         <v>20</v>
       </c>
       <c r="G42" s="51" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H42" s="52">
         <v>2</v>
@@ -3797,7 +3840,7 @@
       <c r="I42" s="52"/>
       <c r="J42" s="53"/>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" hidden="1">
       <c r="A43" s="49" t="s">
         <v>52</v>
       </c>
@@ -3815,7 +3858,7 @@
         <v>20</v>
       </c>
       <c r="G43" s="51" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H43" s="52">
         <v>2</v>
@@ -3823,7 +3866,7 @@
       <c r="I43" s="52"/>
       <c r="J43" s="53"/>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" hidden="1">
       <c r="A44" s="49" t="s">
         <v>52</v>
       </c>
@@ -3841,7 +3884,7 @@
         <v>20</v>
       </c>
       <c r="G44" s="51" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H44" s="52">
         <v>2</v>
@@ -3858,16 +3901,16 @@
       </c>
       <c r="C45" s="50"/>
       <c r="D45" s="50" t="s">
-        <v>129</v>
+        <v>243</v>
       </c>
       <c r="E45" s="51" t="s">
         <v>19</v>
       </c>
       <c r="F45" s="51" t="s">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="G45" s="51" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H45" s="52">
         <v>3</v>
@@ -3875,16 +3918,16 @@
       <c r="I45" s="52"/>
       <c r="J45" s="53"/>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" hidden="1">
       <c r="A46" s="54" t="s">
         <v>41</v>
       </c>
       <c r="B46" s="55" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C46" s="55"/>
       <c r="D46" s="55" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E46" s="56" t="s">
         <v>19</v>
@@ -3893,7 +3936,7 @@
         <v>20</v>
       </c>
       <c r="G46" s="56" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H46" s="57">
         <v>0.5</v>
@@ -3901,16 +3944,16 @@
       <c r="I46" s="57"/>
       <c r="J46" s="58"/>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" hidden="1">
       <c r="A47" s="54" t="s">
         <v>41</v>
       </c>
       <c r="B47" s="55" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C47" s="55"/>
       <c r="D47" s="55" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E47" s="56" t="s">
         <v>19</v>
@@ -3919,7 +3962,7 @@
         <v>20</v>
       </c>
       <c r="G47" s="56" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H47" s="57">
         <v>0.5</v>
@@ -3936,7 +3979,7 @@
       </c>
       <c r="C48" s="55"/>
       <c r="D48" s="55" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E48" s="56" t="s">
         <v>19</v>
@@ -3962,7 +4005,7 @@
       </c>
       <c r="C49" s="55"/>
       <c r="D49" s="55" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E49" s="56" t="s">
         <v>19</v>
@@ -3979,7 +4022,7 @@
       <c r="I49" s="57"/>
       <c r="J49" s="58"/>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" hidden="1">
       <c r="A50" s="54" t="s">
         <v>41</v>
       </c>
@@ -3988,10 +4031,10 @@
       </c>
       <c r="C50" s="55"/>
       <c r="D50" s="55" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E50" s="56" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F50" s="56" t="s">
         <v>20</v>
@@ -4004,7 +4047,7 @@
       </c>
       <c r="I50" s="57"/>
       <c r="J50" s="58" t="s">
-        <v>136</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -4012,11 +4055,11 @@
         <v>50</v>
       </c>
       <c r="B51" s="60" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C51" s="60"/>
       <c r="D51" s="60" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E51" s="61" t="s">
         <v>19</v>
@@ -4025,7 +4068,7 @@
         <v>20</v>
       </c>
       <c r="G51" s="61" t="s">
-        <v>21</v>
+        <v>248</v>
       </c>
       <c r="H51" s="62">
         <v>5</v>
@@ -4038,11 +4081,11 @@
         <v>50</v>
       </c>
       <c r="B52" s="60" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C52" s="60"/>
       <c r="D52" s="60" t="s">
-        <v>139</v>
+        <v>245</v>
       </c>
       <c r="E52" s="61" t="s">
         <v>19</v>
@@ -4054,21 +4097,23 @@
         <v>21</v>
       </c>
       <c r="H52" s="62">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I52" s="62"/>
-      <c r="J52" s="63"/>
+      <c r="J52" s="63" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="59" t="s">
         <v>50</v>
       </c>
       <c r="B53" s="60" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C53" s="60"/>
       <c r="D53" s="60" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E53" s="61" t="s">
         <v>19</v>
@@ -4084,7 +4129,7 @@
       </c>
       <c r="I53" s="62"/>
       <c r="J53" s="63" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -4092,11 +4137,11 @@
         <v>50</v>
       </c>
       <c r="B54" s="60" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C54" s="60"/>
       <c r="D54" s="60" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E54" s="61" t="s">
         <v>19</v>
@@ -4112,19 +4157,19 @@
       </c>
       <c r="I54" s="62"/>
       <c r="J54" s="63" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" hidden="1">
       <c r="A55" s="59" t="s">
         <v>50</v>
       </c>
       <c r="B55" s="60" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C55" s="60"/>
       <c r="D55" s="60" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E55" s="61" t="s">
         <v>19</v>
@@ -4133,7 +4178,7 @@
         <v>20</v>
       </c>
       <c r="G55" s="61" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H55" s="62">
         <v>3</v>
@@ -4141,19 +4186,19 @@
       <c r="I55" s="62"/>
       <c r="J55" s="63"/>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" hidden="1">
       <c r="A56" s="59" t="s">
         <v>50</v>
       </c>
       <c r="B56" s="60" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C56" s="60"/>
       <c r="D56" s="60" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E56" s="61" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F56" s="61" t="s">
         <v>20</v>
@@ -4167,16 +4212,16 @@
       <c r="I56" s="62"/>
       <c r="J56" s="63"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" hidden="1">
       <c r="A57" s="59" t="s">
         <v>50</v>
       </c>
       <c r="B57" s="60" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C57" s="60"/>
       <c r="D57" s="60" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E57" s="61" t="s">
         <v>19</v>
@@ -4185,7 +4230,7 @@
         <v>20</v>
       </c>
       <c r="G57" s="61" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H57" s="62">
         <v>0.5</v>
@@ -4193,16 +4238,16 @@
       <c r="I57" s="62"/>
       <c r="J57" s="63"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" hidden="1">
       <c r="A58" s="59" t="s">
         <v>50</v>
       </c>
       <c r="B58" s="60" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C58" s="60"/>
       <c r="D58" s="60" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E58" s="61" t="s">
         <v>19</v>
@@ -4211,7 +4256,7 @@
         <v>20</v>
       </c>
       <c r="G58" s="61" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H58" s="62">
         <v>0.5</v>
@@ -4219,16 +4264,16 @@
       <c r="I58" s="62"/>
       <c r="J58" s="63"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" hidden="1">
       <c r="A59" s="59" t="s">
         <v>50</v>
       </c>
       <c r="B59" s="60" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C59" s="60"/>
       <c r="D59" s="60" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E59" s="61" t="s">
         <v>26</v>
@@ -4254,7 +4299,7 @@
       </c>
       <c r="C60" s="60"/>
       <c r="D60" s="60" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E60" s="61" t="s">
         <v>19</v>
@@ -4263,7 +4308,7 @@
         <v>20</v>
       </c>
       <c r="G60" s="61" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H60" s="62">
         <v>3</v>
@@ -4280,7 +4325,7 @@
       </c>
       <c r="C61" s="60"/>
       <c r="D61" s="60" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E61" s="61" t="s">
         <v>19</v>
@@ -4306,7 +4351,7 @@
       </c>
       <c r="C62" s="60"/>
       <c r="D62" s="60" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E62" s="61" t="s">
         <v>19</v>
@@ -4323,16 +4368,16 @@
       <c r="I62" s="62"/>
       <c r="J62" s="63"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" hidden="1">
       <c r="A63" s="59" t="s">
         <v>50</v>
       </c>
       <c r="B63" s="60" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C63" s="60"/>
       <c r="D63" s="60" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E63" s="61" t="s">
         <v>26</v>
@@ -4348,19 +4393,19 @@
       </c>
       <c r="I63" s="62"/>
       <c r="J63" s="63" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" hidden="1">
       <c r="A64" s="59" t="s">
         <v>50</v>
       </c>
       <c r="B64" s="60" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C64" s="60"/>
       <c r="D64" s="60" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E64" s="61" t="s">
         <v>26</v>
@@ -4377,16 +4422,16 @@
       <c r="I64" s="62"/>
       <c r="J64" s="63"/>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" hidden="1">
       <c r="A65" s="59" t="s">
         <v>50</v>
       </c>
       <c r="B65" s="60" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C65" s="60"/>
       <c r="D65" s="60" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E65" s="61" t="s">
         <v>26</v>
@@ -4402,19 +4447,19 @@
       </c>
       <c r="I65" s="62"/>
       <c r="J65" s="63" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" hidden="1">
       <c r="A66" s="59" t="s">
         <v>50</v>
       </c>
       <c r="B66" s="60" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C66" s="60"/>
       <c r="D66" s="60" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E66" s="61" t="s">
         <v>26</v>
@@ -4431,16 +4476,16 @@
       <c r="I66" s="62"/>
       <c r="J66" s="63"/>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" hidden="1">
       <c r="A67" s="59" t="s">
         <v>50</v>
       </c>
       <c r="B67" s="60" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C67" s="60"/>
       <c r="D67" s="60" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E67" s="61" t="s">
         <v>26</v>
@@ -4457,7 +4502,7 @@
       <c r="I67" s="62"/>
       <c r="J67" s="63"/>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" hidden="1">
       <c r="A68" s="59" t="s">
         <v>50</v>
       </c>
@@ -4466,7 +4511,7 @@
       </c>
       <c r="C68" s="60"/>
       <c r="D68" s="60" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E68" s="61" t="s">
         <v>26</v>
@@ -4482,10 +4527,10 @@
       </c>
       <c r="I68" s="62"/>
       <c r="J68" s="63" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" hidden="1">
       <c r="A69" s="59" t="s">
         <v>50</v>
       </c>
@@ -4494,7 +4539,7 @@
       </c>
       <c r="C69" s="60"/>
       <c r="D69" s="60" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E69" s="61" t="s">
         <v>26</v>
@@ -4510,10 +4555,10 @@
       </c>
       <c r="I69" s="62"/>
       <c r="J69" s="63" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" hidden="1">
       <c r="A70" s="59" t="s">
         <v>50</v>
       </c>
@@ -4522,7 +4567,7 @@
       </c>
       <c r="C70" s="60"/>
       <c r="D70" s="60" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E70" s="61" t="s">
         <v>26</v>
@@ -4538,10 +4583,10 @@
       </c>
       <c r="I70" s="62"/>
       <c r="J70" s="63" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" hidden="1">
       <c r="A71" s="59" t="s">
         <v>50</v>
       </c>
@@ -4550,7 +4595,7 @@
       </c>
       <c r="C71" s="60"/>
       <c r="D71" s="60" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E71" s="61" t="s">
         <v>26</v>
@@ -4566,10 +4611,10 @@
       </c>
       <c r="I71" s="62"/>
       <c r="J71" s="63" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" hidden="1">
       <c r="A72" s="59" t="s">
         <v>50</v>
       </c>
@@ -4578,7 +4623,7 @@
       </c>
       <c r="C72" s="60"/>
       <c r="D72" s="60" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E72" s="61" t="s">
         <v>26</v>
@@ -4594,10 +4639,10 @@
       </c>
       <c r="I72" s="62"/>
       <c r="J72" s="63" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" hidden="1">
       <c r="A73" s="59" t="s">
         <v>50</v>
       </c>
@@ -4606,7 +4651,7 @@
       </c>
       <c r="C73" s="60"/>
       <c r="D73" s="60" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E73" s="61" t="s">
         <v>26</v>
@@ -4622,10 +4667,10 @@
       </c>
       <c r="I73" s="62"/>
       <c r="J73" s="63" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" hidden="1">
       <c r="A74" s="59" t="s">
         <v>50</v>
       </c>
@@ -4634,7 +4679,7 @@
       </c>
       <c r="C74" s="60"/>
       <c r="D74" s="60" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E74" s="61" t="s">
         <v>26</v>
@@ -4651,7 +4696,7 @@
       <c r="I74" s="62"/>
       <c r="J74" s="63"/>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" hidden="1">
       <c r="A75" s="59" t="s">
         <v>50</v>
       </c>
@@ -4660,7 +4705,7 @@
       </c>
       <c r="C75" s="60"/>
       <c r="D75" s="60" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E75" s="61" t="s">
         <v>26</v>
@@ -4677,7 +4722,7 @@
       <c r="I75" s="62"/>
       <c r="J75" s="63"/>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" hidden="1">
       <c r="A76" s="59" t="s">
         <v>50</v>
       </c>
@@ -4686,7 +4731,7 @@
       </c>
       <c r="C76" s="60"/>
       <c r="D76" s="60" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E76" s="61" t="s">
         <v>26</v>
@@ -4703,16 +4748,16 @@
       <c r="I76" s="62"/>
       <c r="J76" s="63"/>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" hidden="1">
       <c r="A77" s="64" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B77" s="65" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C77" s="65"/>
       <c r="D77" s="65" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E77" s="66" t="s">
         <v>19</v>
@@ -4721,7 +4766,7 @@
         <v>20</v>
       </c>
       <c r="G77" s="66" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H77" s="67">
         <v>1</v>
@@ -4731,14 +4776,14 @@
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="64" t="s">
+        <v>171</v>
+      </c>
+      <c r="B78" s="65" t="s">
         <v>174</v>
-      </c>
-      <c r="B78" s="65" t="s">
-        <v>177</v>
       </c>
       <c r="C78" s="65"/>
       <c r="D78" s="65" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E78" s="66" t="s">
         <v>19</v>
@@ -4747,7 +4792,7 @@
         <v>20</v>
       </c>
       <c r="G78" s="66" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="H78" s="67">
         <v>1</v>
@@ -4757,14 +4802,14 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="64" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B79" s="65" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C79" s="65"/>
       <c r="D79" s="65" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E79" s="66" t="s">
         <v>19</v>
@@ -4773,7 +4818,7 @@
         <v>20</v>
       </c>
       <c r="G79" s="66" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="H79" s="67">
         <v>1</v>
@@ -4783,14 +4828,14 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="64" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B80" s="65" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C80" s="65"/>
       <c r="D80" s="65" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E80" s="66" t="s">
         <v>19</v>
@@ -4799,26 +4844,26 @@
         <v>20</v>
       </c>
       <c r="G80" s="66" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="H80" s="67">
         <v>1</v>
       </c>
       <c r="I80" s="67"/>
       <c r="J80" s="68" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="64" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B81" s="65" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C81" s="65"/>
       <c r="D81" s="65" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E81" s="66" t="s">
         <v>19</v>
@@ -4827,7 +4872,7 @@
         <v>20</v>
       </c>
       <c r="G81" s="66" t="s">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="H81" s="67">
         <v>1</v>
@@ -4835,16 +4880,16 @@
       <c r="I81" s="67"/>
       <c r="J81" s="68"/>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" hidden="1">
       <c r="A82" s="69" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B82" s="70" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C82" s="70"/>
       <c r="D82" s="70" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E82" s="71" t="s">
         <v>26</v>
@@ -4853,7 +4898,7 @@
         <v>20</v>
       </c>
       <c r="G82" s="71" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H82" s="72">
         <v>1</v>
@@ -4861,16 +4906,16 @@
       <c r="I82" s="72"/>
       <c r="J82" s="73"/>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" hidden="1">
       <c r="A83" s="69" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B83" s="70" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C83" s="70"/>
       <c r="D83" s="70" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E83" s="71" t="s">
         <v>26</v>
@@ -4879,7 +4924,7 @@
         <v>20</v>
       </c>
       <c r="G83" s="71" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H83" s="72">
         <v>1</v>
@@ -4887,16 +4932,16 @@
       <c r="I83" s="72"/>
       <c r="J83" s="73"/>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" hidden="1">
       <c r="A84" s="69" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B84" s="70" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C84" s="70"/>
       <c r="D84" s="70" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E84" s="71" t="s">
         <v>26</v>
@@ -4913,16 +4958,16 @@
       <c r="I84" s="72"/>
       <c r="J84" s="73"/>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" hidden="1">
       <c r="A85" s="69" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B85" s="70" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C85" s="70"/>
       <c r="D85" s="70" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E85" s="71" t="s">
         <v>26</v>
@@ -4939,7 +4984,7 @@
       <c r="I85" s="72"/>
       <c r="J85" s="73"/>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" hidden="1">
       <c r="A86" s="74" t="s">
         <v>33</v>
       </c>
@@ -4965,7 +5010,7 @@
       <c r="I86" s="77"/>
       <c r="J86" s="78"/>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" hidden="1">
       <c r="A87" s="74" t="s">
         <v>33</v>
       </c>
@@ -4974,7 +5019,7 @@
       </c>
       <c r="C87" s="75"/>
       <c r="D87" s="75" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E87" s="76" t="s">
         <v>26</v>
@@ -4990,10 +5035,10 @@
       </c>
       <c r="I87" s="77"/>
       <c r="J87" s="78" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" hidden="1">
       <c r="A88" s="74" t="s">
         <v>33</v>
       </c>
@@ -5002,7 +5047,7 @@
       </c>
       <c r="C88" s="75"/>
       <c r="D88" s="75" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E88" s="76" t="s">
         <v>26</v>
@@ -5019,7 +5064,7 @@
       <c r="I88" s="77"/>
       <c r="J88" s="78"/>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" hidden="1">
       <c r="A89" s="74" t="s">
         <v>33</v>
       </c>
@@ -5028,7 +5073,7 @@
       </c>
       <c r="C89" s="75"/>
       <c r="D89" s="75" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E89" s="76" t="s">
         <v>26</v>
@@ -5045,7 +5090,7 @@
       <c r="I89" s="77"/>
       <c r="J89" s="78"/>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" hidden="1">
       <c r="A90" s="74" t="s">
         <v>33</v>
       </c>
@@ -5071,7 +5116,7 @@
       <c r="I90" s="77"/>
       <c r="J90" s="78"/>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" hidden="1">
       <c r="A91" s="74" t="s">
         <v>33</v>
       </c>
@@ -5080,7 +5125,7 @@
       </c>
       <c r="C91" s="75"/>
       <c r="D91" s="75" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E91" s="76" t="s">
         <v>26</v>
@@ -5097,7 +5142,7 @@
       <c r="I91" s="77"/>
       <c r="J91" s="78"/>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" hidden="1">
       <c r="A92" s="74" t="s">
         <v>33</v>
       </c>
@@ -5106,7 +5151,7 @@
       </c>
       <c r="C92" s="75"/>
       <c r="D92" s="75" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E92" s="76" t="s">
         <v>26</v>
@@ -5122,10 +5167,10 @@
       </c>
       <c r="I92" s="77"/>
       <c r="J92" s="78" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" hidden="1">
       <c r="A93" s="74" t="s">
         <v>33</v>
       </c>
@@ -5134,7 +5179,7 @@
       </c>
       <c r="C93" s="75"/>
       <c r="D93" s="75" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E93" s="76" t="s">
         <v>26</v>
@@ -5151,7 +5196,7 @@
       <c r="I93" s="77"/>
       <c r="J93" s="78"/>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" hidden="1">
       <c r="A94" s="74" t="s">
         <v>33</v>
       </c>
@@ -5160,7 +5205,7 @@
       </c>
       <c r="C94" s="75"/>
       <c r="D94" s="75" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E94" s="76" t="s">
         <v>26</v>
@@ -5177,16 +5222,16 @@
       <c r="I94" s="77"/>
       <c r="J94" s="78"/>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" hidden="1">
       <c r="A95" s="74" t="s">
         <v>33</v>
       </c>
       <c r="B95" s="75" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C95" s="75"/>
       <c r="D95" s="75" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E95" s="76" t="s">
         <v>26</v>
@@ -5203,7 +5248,7 @@
       <c r="I95" s="77"/>
       <c r="J95" s="78"/>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" hidden="1">
       <c r="A96" s="79" t="s">
         <v>35</v>
       </c>
@@ -5212,7 +5257,7 @@
       </c>
       <c r="C96" s="80"/>
       <c r="D96" s="80" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E96" s="81" t="s">
         <v>37</v>
@@ -5229,7 +5274,7 @@
       <c r="I96" s="82"/>
       <c r="J96" s="83"/>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" hidden="1">
       <c r="A97" s="79" t="s">
         <v>35</v>
       </c>
@@ -5238,7 +5283,7 @@
       </c>
       <c r="C97" s="80"/>
       <c r="D97" s="80" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E97" s="81" t="s">
         <v>37</v>
@@ -5255,16 +5300,16 @@
       <c r="I97" s="82"/>
       <c r="J97" s="83"/>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" hidden="1">
       <c r="A98" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B98" s="80" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C98" s="80"/>
       <c r="D98" s="80" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E98" s="81" t="s">
         <v>37</v>
@@ -5281,7 +5326,7 @@
       <c r="I98" s="82"/>
       <c r="J98" s="83"/>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" hidden="1">
       <c r="A99" s="79" t="s">
         <v>35</v>
       </c>
@@ -5290,7 +5335,7 @@
       </c>
       <c r="C99" s="80"/>
       <c r="D99" s="80" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E99" s="81" t="s">
         <v>37</v>
@@ -5306,10 +5351,10 @@
       </c>
       <c r="I99" s="82"/>
       <c r="J99" s="83" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" hidden="1">
       <c r="A100" s="79" t="s">
         <v>35</v>
       </c>
@@ -5318,7 +5363,7 @@
       </c>
       <c r="C100" s="80"/>
       <c r="D100" s="80" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E100" s="81" t="s">
         <v>37</v>
@@ -5334,10 +5379,10 @@
       </c>
       <c r="I100" s="82"/>
       <c r="J100" s="83" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" hidden="1">
       <c r="A101" s="79" t="s">
         <v>35</v>
       </c>
@@ -5362,10 +5407,10 @@
       </c>
       <c r="I101" s="82"/>
       <c r="J101" s="83" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" hidden="1">
       <c r="A102" s="79" t="s">
         <v>35</v>
       </c>
@@ -5374,7 +5419,7 @@
       </c>
       <c r="C102" s="80"/>
       <c r="D102" s="80" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E102" s="81" t="s">
         <v>37</v>
@@ -5390,19 +5435,19 @@
       </c>
       <c r="I102" s="82"/>
       <c r="J102" s="83" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" hidden="1">
       <c r="A103" s="84" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B103" s="85" t="s">
         <v>40</v>
       </c>
       <c r="C103" s="85"/>
       <c r="D103" s="85" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E103" s="86" t="s">
         <v>37</v>
@@ -5419,16 +5464,16 @@
       <c r="I103" s="87"/>
       <c r="J103" s="88"/>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" hidden="1">
       <c r="A104" s="84" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B104" s="85" t="s">
         <v>40</v>
       </c>
       <c r="C104" s="85"/>
       <c r="D104" s="85" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E104" s="86" t="s">
         <v>37</v>
@@ -5445,16 +5490,16 @@
       <c r="I104" s="87"/>
       <c r="J104" s="88"/>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" hidden="1">
       <c r="A105" s="84" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B105" s="85" t="s">
         <v>40</v>
       </c>
       <c r="C105" s="85"/>
       <c r="D105" s="85" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E105" s="86" t="s">
         <v>37</v>
@@ -5471,16 +5516,16 @@
       <c r="I105" s="87"/>
       <c r="J105" s="88"/>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" hidden="1">
       <c r="A106" s="84" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B106" s="85" t="s">
         <v>40</v>
       </c>
       <c r="C106" s="85"/>
       <c r="D106" s="85" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E106" s="86" t="s">
         <v>37</v>
@@ -5497,16 +5542,16 @@
       <c r="I106" s="87"/>
       <c r="J106" s="88"/>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" hidden="1">
       <c r="A107" s="84" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B107" s="85" t="s">
         <v>40</v>
       </c>
       <c r="C107" s="85"/>
       <c r="D107" s="85" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E107" s="86" t="s">
         <v>37</v>
@@ -5523,16 +5568,16 @@
       <c r="I107" s="87"/>
       <c r="J107" s="88"/>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" hidden="1">
       <c r="A108" s="84" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B108" s="85" t="s">
         <v>38</v>
       </c>
       <c r="C108" s="85"/>
       <c r="D108" s="85" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E108" s="86" t="s">
         <v>37</v>
@@ -5549,16 +5594,16 @@
       <c r="I108" s="87"/>
       <c r="J108" s="88"/>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" hidden="1">
       <c r="A109" s="84" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B109" s="85" t="s">
         <v>38</v>
       </c>
       <c r="C109" s="85"/>
       <c r="D109" s="85" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E109" s="86" t="s">
         <v>37</v>
@@ -5575,16 +5620,16 @@
       <c r="I109" s="87"/>
       <c r="J109" s="88"/>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" hidden="1">
       <c r="A110" s="84" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B110" s="85" t="s">
         <v>38</v>
       </c>
       <c r="C110" s="85"/>
       <c r="D110" s="85" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E110" s="86" t="s">
         <v>37</v>
@@ -5601,16 +5646,16 @@
       <c r="I110" s="87"/>
       <c r="J110" s="88"/>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" hidden="1">
       <c r="A111" s="84" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B111" s="85" t="s">
         <v>39</v>
       </c>
       <c r="C111" s="85"/>
       <c r="D111" s="85" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E111" s="86" t="s">
         <v>37</v>
@@ -5619,7 +5664,7 @@
         <v>20</v>
       </c>
       <c r="G111" s="86" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H111" s="87">
         <v>1</v>
@@ -5627,16 +5672,16 @@
       <c r="I111" s="87"/>
       <c r="J111" s="88"/>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" hidden="1">
       <c r="A112" s="84" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B112" s="85" t="s">
         <v>39</v>
       </c>
       <c r="C112" s="85"/>
       <c r="D112" s="85" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E112" s="86" t="s">
         <v>37</v>
@@ -5653,16 +5698,16 @@
       <c r="I112" s="87"/>
       <c r="J112" s="88"/>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" hidden="1">
       <c r="A113" s="89" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B113" s="90" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C113" s="90"/>
       <c r="D113" s="90" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E113" s="91" t="s">
         <v>37</v>
@@ -5673,24 +5718,24 @@
       <c r="G113" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="H113" s="87" t="s">
-        <v>244</v>
+      <c r="H113" s="87">
+        <v>10</v>
       </c>
       <c r="I113" s="92"/>
       <c r="J113" s="93" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" hidden="1">
       <c r="A114" s="89" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B114" s="90" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C114" s="90"/>
       <c r="D114" s="90" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E114" s="91" t="s">
         <v>37</v>
@@ -5701,22 +5746,22 @@
       <c r="G114" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="H114" s="87" t="s">
-        <v>244</v>
+      <c r="H114" s="87">
+        <v>10</v>
       </c>
       <c r="I114" s="92"/>
       <c r="J114" s="93"/>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" hidden="1">
       <c r="A115" s="89" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B115" s="90" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C115" s="90"/>
       <c r="D115" s="90" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E115" s="91" t="s">
         <v>37</v>
@@ -5727,22 +5772,22 @@
       <c r="G115" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="H115" s="87" t="s">
-        <v>244</v>
+      <c r="H115" s="87">
+        <v>10</v>
       </c>
       <c r="I115" s="92"/>
       <c r="J115" s="93"/>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" hidden="1">
       <c r="A116" s="89" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B116" s="90" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C116" s="90"/>
       <c r="D116" s="90" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E116" s="91" t="s">
         <v>48</v>
@@ -5759,7 +5804,7 @@
       <c r="I116" s="92"/>
       <c r="J116" s="93"/>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" hidden="1">
       <c r="A117" s="94"/>
       <c r="B117" s="94"/>
       <c r="C117" s="94"/>
@@ -5771,7 +5816,7 @@
       <c r="G117" s="94"/>
       <c r="H117" s="95">
         <f>SUM(H2:H116)</f>
-        <v>238.5</v>
+        <v>271.5</v>
       </c>
       <c r="I117" s="95">
         <f>SUM(I2:I116)</f>
@@ -5780,7 +5825,19 @@
       <c r="J117" s="94"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J116" xr:uid="{F591B56F-9C16-43FE-9B5C-FD4AC86E6A15}"/>
+  <autoFilter ref="A1:J117" xr:uid="{F591B56F-9C16-43FE-9B5C-FD4AC86E6A15}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="プロト"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6">
+      <filters>
+        <filter val="進行中"/>
+        <filter val="未着手"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="4"/>
   <conditionalFormatting sqref="H2:H116">
     <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
@@ -5856,7 +5913,7 @@
       </c>
       <c r="B7" s="7">
         <f ca="1">MAX(0,B4-TODAY())</f>
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -5891,21 +5948,22 @@
     </row>
     <row r="3" spans="1:2">
       <c r="B3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/WinterGame2026_コスト表.xlsx
+++ b/WinterGame2026_コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kudosyota\Desktop\GitHub\WinterGame2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skoto\Git\WinterGame2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD58E1F-2FAF-43D9-9E52-3354C4FBC3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088932F6-8F59-46DF-AA25-4B845A4003EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8B56E59A-6A48-4E9E-98F0-BB372CB837AE}"/>
+    <workbookView xWindow="8385" yWindow="0" windowWidth="16095" windowHeight="15585" activeTab="4" xr2:uid="{8B56E59A-6A48-4E9E-98F0-BB372CB837AE}"/>
   </bookViews>
   <sheets>
     <sheet name="集計" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="256">
   <si>
     <t>WinterGame2026 設定</t>
   </si>
@@ -881,6 +881,82 @@
   </si>
   <si>
     <t>進行中</t>
+  </si>
+  <si>
+    <t>エイリアンの仕様</t>
+    <rPh sb="6" eb="8">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>浮遊している</t>
+    <rPh sb="0" eb="2">
+      <t>フユウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>遠距離攻撃をする(ブレス攻撃)</t>
+    <rPh sb="0" eb="3">
+      <t>エンキョリ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>踵落としで叩き落せる</t>
+    <rPh sb="0" eb="2">
+      <t>カカトオ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タタ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>デカイ手の攻撃でも落とせる</t>
+    <rPh sb="3" eb="4">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>攻撃したあとプレイヤーから距離をとって様子をみる</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヨウス</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>攻撃の予兆がある</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨチョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -5913,7 +5989,7 @@
       </c>
       <c r="B7" s="7">
         <f ca="1">MAX(0,B4-TODAY())</f>
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -5938,7 +6014,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1D838DA-6C01-4DFD-980E-9C45A10CBCD9}">
-  <dimension ref="A2:B5"/>
+  <dimension ref="A2:B16"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:2">
@@ -5959,6 +6035,46 @@
     <row r="5" spans="1:2">
       <c r="B5" t="s">
         <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="B11" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="B12" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="B13" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="B14" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="B16" t="s">
+        <v>255</v>
       </c>
     </row>
   </sheetData>

--- a/WinterGame2026_コスト表.xlsx
+++ b/WinterGame2026_コスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skoto\Git\WinterGame2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088932F6-8F59-46DF-AA25-4B845A4003EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D4BE2A-599B-4B94-A23A-5646E17EC773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8385" yWindow="0" windowWidth="16095" windowHeight="15585" activeTab="4" xr2:uid="{8B56E59A-6A48-4E9E-98F0-BB372CB837AE}"/>
+    <workbookView xWindow="8385" yWindow="0" windowWidth="16095" windowHeight="10170" activeTab="2" xr2:uid="{8B56E59A-6A48-4E9E-98F0-BB372CB837AE}"/>
   </bookViews>
   <sheets>
     <sheet name="集計" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="255">
   <si>
     <t>WinterGame2026 設定</t>
   </si>
@@ -878,9 +878,6 @@
   </si>
   <si>
     <t>完了</t>
-  </si>
-  <si>
-    <t>進行中</t>
   </si>
   <si>
     <t>エイリアンの仕様</t>
@@ -2007,7 +2004,7 @@
       </c>
       <c r="C4" s="7">
         <f>COUNTIFS(タスク一覧!$E$2:$E$116,$A4,タスク一覧!$G$2:$G$116,"完了")</f>
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D4" s="7">
         <f>SUMPRODUCT((タスク一覧!$E$2:$E$116=$A4)*(タスク一覧!$H$2:$H$116=0))</f>
@@ -2023,15 +2020,15 @@
       </c>
       <c r="G4" s="97">
         <f>SUMIFS(タスク一覧!$H$2:$H$116,タスク一覧!$E$2:$E$116,$A4,タスク一覧!$G$2:$G$116,"完了")</f>
-        <v>77.5</v>
+        <v>111</v>
       </c>
       <c r="H4" s="12">
         <f>IFERROR(G4/E4,0)</f>
-        <v>0.53633217993079585</v>
+        <v>0.76816608996539792</v>
       </c>
       <c r="I4" s="99">
         <f>SUMIFS(タスク一覧!$I$2:$I$116,タスク一覧!$E$2:$E$116,$A4,タスク一覧!$G$2:$G$116,"完了")-G4</f>
-        <v>-77.5</v>
+        <v>-111</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2155,7 +2152,7 @@
       </c>
       <c r="C8" s="96">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D8" s="96">
         <f t="shared" si="0"/>
@@ -2171,15 +2168,15 @@
       </c>
       <c r="G8" s="98">
         <f t="shared" si="0"/>
-        <v>80.5</v>
+        <v>114</v>
       </c>
       <c r="H8" s="14">
         <f>IFERROR(G8/E8,0)</f>
-        <v>0.2965009208103131</v>
+        <v>0.41988950276243092</v>
       </c>
       <c r="I8" s="100">
         <f>SUM(I4:I7)</f>
-        <v>-80.5</v>
+        <v>-114</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3124,7 +3121,7 @@
         <v>20</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>21</v>
+        <v>237</v>
       </c>
       <c r="H12" s="32">
         <v>5</v>
@@ -3150,7 +3147,7 @@
         <v>20</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>21</v>
+        <v>236</v>
       </c>
       <c r="H13" s="32">
         <v>0.5</v>
@@ -3548,7 +3545,7 @@
       <c r="I28" s="37"/>
       <c r="J28" s="38"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" hidden="1">
       <c r="A29" s="34" t="s">
         <v>24</v>
       </c>
@@ -3566,7 +3563,7 @@
         <v>20</v>
       </c>
       <c r="G29" s="36" t="s">
-        <v>21</v>
+        <v>236</v>
       </c>
       <c r="H29" s="37">
         <v>4</v>
@@ -3678,7 +3675,7 @@
       <c r="I33" s="42"/>
       <c r="J33" s="43"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" hidden="1">
       <c r="A34" s="39" t="s">
         <v>23</v>
       </c>
@@ -3696,7 +3693,7 @@
         <v>20</v>
       </c>
       <c r="G34" s="41" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H34" s="42">
         <v>4</v>
@@ -4090,7 +4087,7 @@
         <v>20</v>
       </c>
       <c r="G49" s="56" t="s">
-        <v>21</v>
+        <v>236</v>
       </c>
       <c r="H49" s="57">
         <v>2</v>
@@ -4126,7 +4123,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" hidden="1">
       <c r="A51" s="59" t="s">
         <v>50</v>
       </c>
@@ -4144,7 +4141,7 @@
         <v>20</v>
       </c>
       <c r="G51" s="61" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="H51" s="62">
         <v>5</v>
@@ -4152,7 +4149,7 @@
       <c r="I51" s="62"/>
       <c r="J51" s="63"/>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" hidden="1">
       <c r="A52" s="59" t="s">
         <v>50</v>
       </c>
@@ -4170,7 +4167,7 @@
         <v>20</v>
       </c>
       <c r="G52" s="61" t="s">
-        <v>21</v>
+        <v>236</v>
       </c>
       <c r="H52" s="62">
         <v>10</v>
@@ -4180,7 +4177,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" hidden="1">
       <c r="A53" s="59" t="s">
         <v>50</v>
       </c>
@@ -4198,7 +4195,7 @@
         <v>20</v>
       </c>
       <c r="G53" s="61" t="s">
-        <v>21</v>
+        <v>236</v>
       </c>
       <c r="H53" s="62">
         <v>2</v>
@@ -4208,7 +4205,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" hidden="1">
       <c r="A54" s="59" t="s">
         <v>50</v>
       </c>
@@ -4226,7 +4223,7 @@
         <v>20</v>
       </c>
       <c r="G54" s="61" t="s">
-        <v>21</v>
+        <v>236</v>
       </c>
       <c r="H54" s="62">
         <v>1</v>
@@ -4366,7 +4363,7 @@
       <c r="I59" s="62"/>
       <c r="J59" s="63"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" hidden="1">
       <c r="A60" s="59" t="s">
         <v>50</v>
       </c>
@@ -4384,7 +4381,7 @@
         <v>20</v>
       </c>
       <c r="G60" s="61" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H60" s="62">
         <v>3</v>
@@ -4392,7 +4389,7 @@
       <c r="I60" s="62"/>
       <c r="J60" s="63"/>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" hidden="1">
       <c r="A61" s="59" t="s">
         <v>50</v>
       </c>
@@ -4410,7 +4407,7 @@
         <v>20</v>
       </c>
       <c r="G61" s="61" t="s">
-        <v>21</v>
+        <v>236</v>
       </c>
       <c r="H61" s="62">
         <v>2</v>
@@ -4850,7 +4847,7 @@
       <c r="I77" s="67"/>
       <c r="J77" s="68"/>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" hidden="1">
       <c r="A78" s="64" t="s">
         <v>171</v>
       </c>
@@ -4876,7 +4873,7 @@
       <c r="I78" s="67"/>
       <c r="J78" s="68"/>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" hidden="1">
       <c r="A79" s="64" t="s">
         <v>171</v>
       </c>
@@ -4902,7 +4899,7 @@
       <c r="I79" s="67"/>
       <c r="J79" s="68"/>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" hidden="1">
       <c r="A80" s="64" t="s">
         <v>171</v>
       </c>
@@ -4930,7 +4927,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" hidden="1">
       <c r="A81" s="64" t="s">
         <v>171</v>
       </c>
@@ -5766,7 +5763,7 @@
         <v>20</v>
       </c>
       <c r="G112" s="86" t="s">
-        <v>21</v>
+        <v>237</v>
       </c>
       <c r="H112" s="87">
         <v>1</v>
@@ -5989,7 +5986,7 @@
       </c>
       <c r="B7" s="7">
         <f ca="1">MAX(0,B4-TODAY())</f>
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6044,37 +6041,37 @@
     </row>
     <row r="10" spans="1:2">
       <c r="B10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="B11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="B13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/WinterGame2026_コスト表.xlsx
+++ b/WinterGame2026_コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skoto\Git\WinterGame2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kudosyota\Desktop\GitHub\WinterGame2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D4BE2A-599B-4B94-A23A-5646E17EC773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7A5B4A-73A0-4CD0-AD96-210B4CD12FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8385" yWindow="0" windowWidth="16095" windowHeight="10170" activeTab="2" xr2:uid="{8B56E59A-6A48-4E9E-98F0-BB372CB837AE}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8B56E59A-6A48-4E9E-98F0-BB372CB837AE}"/>
   </bookViews>
   <sheets>
     <sheet name="集計" sheetId="1" r:id="rId1"/>
@@ -3129,7 +3129,7 @@
       <c r="I12" s="32"/>
       <c r="J12" s="33"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" hidden="1">
       <c r="A13" s="29" t="s">
         <v>17</v>
       </c>
@@ -4069,7 +4069,7 @@
       <c r="I48" s="57"/>
       <c r="J48" s="58"/>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" hidden="1">
       <c r="A49" s="54" t="s">
         <v>41</v>
       </c>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="B7" s="7">
         <f ca="1">MAX(0,B4-TODAY())</f>
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:2">

--- a/WinterGame2026_コスト表.xlsx
+++ b/WinterGame2026_コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kudosyota\Desktop\GitHub\WinterGame2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skoto\Git\WinterGame2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7A5B4A-73A0-4CD0-AD96-210B4CD12FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B8D14A-50B6-4092-90F1-0A5FB005196C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8B56E59A-6A48-4E9E-98F0-BB372CB837AE}"/>
+    <workbookView xWindow="9060" yWindow="0" windowWidth="16095" windowHeight="10170" activeTab="2" xr2:uid="{8B56E59A-6A48-4E9E-98F0-BB372CB837AE}"/>
   </bookViews>
   <sheets>
     <sheet name="集計" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="259">
   <si>
     <t>WinterGame2026 設定</t>
   </si>
@@ -952,6 +952,34 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>ヨチョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>カメラのロックオン</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>マップを作る</t>
+    <rPh sb="4" eb="5">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>スポーン条件作る</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ボスの設計やる</t>
+    <rPh sb="3" eb="5">
+      <t>セッケイ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -2004,7 +2032,7 @@
       </c>
       <c r="C4" s="7">
         <f>COUNTIFS(タスク一覧!$E$2:$E$116,$A4,タスク一覧!$G$2:$G$116,"完了")</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" s="7">
         <f>SUMPRODUCT((タスク一覧!$E$2:$E$116=$A4)*(タスク一覧!$H$2:$H$116=0))</f>
@@ -2020,15 +2048,15 @@
       </c>
       <c r="G4" s="97">
         <f>SUMIFS(タスク一覧!$H$2:$H$116,タスク一覧!$E$2:$E$116,$A4,タスク一覧!$G$2:$G$116,"完了")</f>
-        <v>111</v>
+        <v>111.5</v>
       </c>
       <c r="H4" s="12">
         <f>IFERROR(G4/E4,0)</f>
-        <v>0.76816608996539792</v>
+        <v>0.77162629757785473</v>
       </c>
       <c r="I4" s="99">
         <f>SUMIFS(タスク一覧!$I$2:$I$116,タスク一覧!$E$2:$E$116,$A4,タスク一覧!$G$2:$G$116,"完了")-G4</f>
-        <v>-111</v>
+        <v>-111.5</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2152,7 +2180,7 @@
       </c>
       <c r="C8" s="96">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" s="96">
         <f t="shared" si="0"/>
@@ -2168,15 +2196,15 @@
       </c>
       <c r="G8" s="98">
         <f t="shared" si="0"/>
-        <v>114</v>
+        <v>114.5</v>
       </c>
       <c r="H8" s="14">
         <f>IFERROR(G8/E8,0)</f>
-        <v>0.41988950276243092</v>
+        <v>0.42173112338858193</v>
       </c>
       <c r="I8" s="100">
         <f>SUM(I4:I7)</f>
-        <v>-114</v>
+        <v>-114.5</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3155,7 +3183,7 @@
       <c r="I13" s="32"/>
       <c r="J13" s="33"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" hidden="1">
       <c r="A14" s="29" t="s">
         <v>17</v>
       </c>
@@ -3173,7 +3201,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="H14" s="32">
         <v>0.5</v>
@@ -4095,7 +4123,7 @@
       <c r="I49" s="57"/>
       <c r="J49" s="58"/>
     </row>
-    <row r="50" spans="1:10" hidden="1">
+    <row r="50" spans="1:10">
       <c r="A50" s="54" t="s">
         <v>41</v>
       </c>
@@ -4259,7 +4287,7 @@
       <c r="I55" s="62"/>
       <c r="J55" s="63"/>
     </row>
-    <row r="56" spans="1:10" hidden="1">
+    <row r="56" spans="1:10">
       <c r="A56" s="59" t="s">
         <v>50</v>
       </c>
@@ -4337,7 +4365,7 @@
       <c r="I58" s="62"/>
       <c r="J58" s="63"/>
     </row>
-    <row r="59" spans="1:10" hidden="1">
+    <row r="59" spans="1:10">
       <c r="A59" s="59" t="s">
         <v>50</v>
       </c>
@@ -4441,7 +4469,7 @@
       <c r="I62" s="62"/>
       <c r="J62" s="63"/>
     </row>
-    <row r="63" spans="1:10" hidden="1">
+    <row r="63" spans="1:10">
       <c r="A63" s="59" t="s">
         <v>50</v>
       </c>
@@ -4469,7 +4497,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1">
+    <row r="64" spans="1:10">
       <c r="A64" s="59" t="s">
         <v>50</v>
       </c>
@@ -4495,7 +4523,7 @@
       <c r="I64" s="62"/>
       <c r="J64" s="63"/>
     </row>
-    <row r="65" spans="1:10" hidden="1">
+    <row r="65" spans="1:10">
       <c r="A65" s="59" t="s">
         <v>50</v>
       </c>
@@ -4523,7 +4551,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1">
+    <row r="66" spans="1:10">
       <c r="A66" s="59" t="s">
         <v>50</v>
       </c>
@@ -4549,7 +4577,7 @@
       <c r="I66" s="62"/>
       <c r="J66" s="63"/>
     </row>
-    <row r="67" spans="1:10" hidden="1">
+    <row r="67" spans="1:10">
       <c r="A67" s="59" t="s">
         <v>50</v>
       </c>
@@ -4575,7 +4603,7 @@
       <c r="I67" s="62"/>
       <c r="J67" s="63"/>
     </row>
-    <row r="68" spans="1:10" hidden="1">
+    <row r="68" spans="1:10">
       <c r="A68" s="59" t="s">
         <v>50</v>
       </c>
@@ -4603,7 +4631,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1">
+    <row r="69" spans="1:10">
       <c r="A69" s="59" t="s">
         <v>50</v>
       </c>
@@ -4631,7 +4659,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1">
+    <row r="70" spans="1:10">
       <c r="A70" s="59" t="s">
         <v>50</v>
       </c>
@@ -4659,7 +4687,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1">
+    <row r="71" spans="1:10">
       <c r="A71" s="59" t="s">
         <v>50</v>
       </c>
@@ -4687,7 +4715,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1">
+    <row r="72" spans="1:10">
       <c r="A72" s="59" t="s">
         <v>50</v>
       </c>
@@ -4715,7 +4743,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1">
+    <row r="73" spans="1:10">
       <c r="A73" s="59" t="s">
         <v>50</v>
       </c>
@@ -4743,7 +4771,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1">
+    <row r="74" spans="1:10">
       <c r="A74" s="59" t="s">
         <v>50</v>
       </c>
@@ -4769,7 +4797,7 @@
       <c r="I74" s="62"/>
       <c r="J74" s="63"/>
     </row>
-    <row r="75" spans="1:10" hidden="1">
+    <row r="75" spans="1:10">
       <c r="A75" s="59" t="s">
         <v>50</v>
       </c>
@@ -4795,7 +4823,7 @@
       <c r="I75" s="62"/>
       <c r="J75" s="63"/>
     </row>
-    <row r="76" spans="1:10" hidden="1">
+    <row r="76" spans="1:10">
       <c r="A76" s="59" t="s">
         <v>50</v>
       </c>
@@ -5005,7 +5033,7 @@
       <c r="I83" s="72"/>
       <c r="J83" s="73"/>
     </row>
-    <row r="84" spans="1:10" hidden="1">
+    <row r="84" spans="1:10">
       <c r="A84" s="69" t="s">
         <v>183</v>
       </c>
@@ -5031,7 +5059,7 @@
       <c r="I84" s="72"/>
       <c r="J84" s="73"/>
     </row>
-    <row r="85" spans="1:10" hidden="1">
+    <row r="85" spans="1:10">
       <c r="A85" s="69" t="s">
         <v>183</v>
       </c>
@@ -5057,7 +5085,7 @@
       <c r="I85" s="72"/>
       <c r="J85" s="73"/>
     </row>
-    <row r="86" spans="1:10" hidden="1">
+    <row r="86" spans="1:10">
       <c r="A86" s="74" t="s">
         <v>33</v>
       </c>
@@ -5083,7 +5111,7 @@
       <c r="I86" s="77"/>
       <c r="J86" s="78"/>
     </row>
-    <row r="87" spans="1:10" hidden="1">
+    <row r="87" spans="1:10">
       <c r="A87" s="74" t="s">
         <v>33</v>
       </c>
@@ -5111,7 +5139,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1">
+    <row r="88" spans="1:10">
       <c r="A88" s="74" t="s">
         <v>33</v>
       </c>
@@ -5137,7 +5165,7 @@
       <c r="I88" s="77"/>
       <c r="J88" s="78"/>
     </row>
-    <row r="89" spans="1:10" hidden="1">
+    <row r="89" spans="1:10">
       <c r="A89" s="74" t="s">
         <v>33</v>
       </c>
@@ -5163,7 +5191,7 @@
       <c r="I89" s="77"/>
       <c r="J89" s="78"/>
     </row>
-    <row r="90" spans="1:10" hidden="1">
+    <row r="90" spans="1:10">
       <c r="A90" s="74" t="s">
         <v>33</v>
       </c>
@@ -5189,7 +5217,7 @@
       <c r="I90" s="77"/>
       <c r="J90" s="78"/>
     </row>
-    <row r="91" spans="1:10" hidden="1">
+    <row r="91" spans="1:10">
       <c r="A91" s="74" t="s">
         <v>33</v>
       </c>
@@ -5215,7 +5243,7 @@
       <c r="I91" s="77"/>
       <c r="J91" s="78"/>
     </row>
-    <row r="92" spans="1:10" hidden="1">
+    <row r="92" spans="1:10">
       <c r="A92" s="74" t="s">
         <v>33</v>
       </c>
@@ -5243,7 +5271,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="93" spans="1:10" hidden="1">
+    <row r="93" spans="1:10">
       <c r="A93" s="74" t="s">
         <v>33</v>
       </c>
@@ -5269,7 +5297,7 @@
       <c r="I93" s="77"/>
       <c r="J93" s="78"/>
     </row>
-    <row r="94" spans="1:10" hidden="1">
+    <row r="94" spans="1:10">
       <c r="A94" s="74" t="s">
         <v>33</v>
       </c>
@@ -5295,7 +5323,7 @@
       <c r="I94" s="77"/>
       <c r="J94" s="78"/>
     </row>
-    <row r="95" spans="1:10" hidden="1">
+    <row r="95" spans="1:10">
       <c r="A95" s="74" t="s">
         <v>33</v>
       </c>
@@ -5321,7 +5349,7 @@
       <c r="I95" s="77"/>
       <c r="J95" s="78"/>
     </row>
-    <row r="96" spans="1:10" hidden="1">
+    <row r="96" spans="1:10">
       <c r="A96" s="79" t="s">
         <v>35</v>
       </c>
@@ -5347,7 +5375,7 @@
       <c r="I96" s="82"/>
       <c r="J96" s="83"/>
     </row>
-    <row r="97" spans="1:10" hidden="1">
+    <row r="97" spans="1:10">
       <c r="A97" s="79" t="s">
         <v>35</v>
       </c>
@@ -5373,7 +5401,7 @@
       <c r="I97" s="82"/>
       <c r="J97" s="83"/>
     </row>
-    <row r="98" spans="1:10" hidden="1">
+    <row r="98" spans="1:10">
       <c r="A98" s="79" t="s">
         <v>35</v>
       </c>
@@ -5399,7 +5427,7 @@
       <c r="I98" s="82"/>
       <c r="J98" s="83"/>
     </row>
-    <row r="99" spans="1:10" hidden="1">
+    <row r="99" spans="1:10">
       <c r="A99" s="79" t="s">
         <v>35</v>
       </c>
@@ -5427,7 +5455,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="100" spans="1:10" hidden="1">
+    <row r="100" spans="1:10">
       <c r="A100" s="79" t="s">
         <v>35</v>
       </c>
@@ -5455,7 +5483,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="101" spans="1:10" hidden="1">
+    <row r="101" spans="1:10">
       <c r="A101" s="79" t="s">
         <v>35</v>
       </c>
@@ -5483,7 +5511,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="102" spans="1:10" hidden="1">
+    <row r="102" spans="1:10">
       <c r="A102" s="79" t="s">
         <v>35</v>
       </c>
@@ -5511,7 +5539,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="103" spans="1:10" hidden="1">
+    <row r="103" spans="1:10">
       <c r="A103" s="84" t="s">
         <v>210</v>
       </c>
@@ -5537,7 +5565,7 @@
       <c r="I103" s="87"/>
       <c r="J103" s="88"/>
     </row>
-    <row r="104" spans="1:10" hidden="1">
+    <row r="104" spans="1:10">
       <c r="A104" s="84" t="s">
         <v>210</v>
       </c>
@@ -5563,7 +5591,7 @@
       <c r="I104" s="87"/>
       <c r="J104" s="88"/>
     </row>
-    <row r="105" spans="1:10" hidden="1">
+    <row r="105" spans="1:10">
       <c r="A105" s="84" t="s">
         <v>210</v>
       </c>
@@ -5589,7 +5617,7 @@
       <c r="I105" s="87"/>
       <c r="J105" s="88"/>
     </row>
-    <row r="106" spans="1:10" hidden="1">
+    <row r="106" spans="1:10">
       <c r="A106" s="84" t="s">
         <v>210</v>
       </c>
@@ -5615,7 +5643,7 @@
       <c r="I106" s="87"/>
       <c r="J106" s="88"/>
     </row>
-    <row r="107" spans="1:10" hidden="1">
+    <row r="107" spans="1:10">
       <c r="A107" s="84" t="s">
         <v>210</v>
       </c>
@@ -5641,7 +5669,7 @@
       <c r="I107" s="87"/>
       <c r="J107" s="88"/>
     </row>
-    <row r="108" spans="1:10" hidden="1">
+    <row r="108" spans="1:10">
       <c r="A108" s="84" t="s">
         <v>210</v>
       </c>
@@ -5667,7 +5695,7 @@
       <c r="I108" s="87"/>
       <c r="J108" s="88"/>
     </row>
-    <row r="109" spans="1:10" hidden="1">
+    <row r="109" spans="1:10">
       <c r="A109" s="84" t="s">
         <v>210</v>
       </c>
@@ -5693,7 +5721,7 @@
       <c r="I109" s="87"/>
       <c r="J109" s="88"/>
     </row>
-    <row r="110" spans="1:10" hidden="1">
+    <row r="110" spans="1:10">
       <c r="A110" s="84" t="s">
         <v>210</v>
       </c>
@@ -5745,7 +5773,7 @@
       <c r="I111" s="87"/>
       <c r="J111" s="88"/>
     </row>
-    <row r="112" spans="1:10" hidden="1">
+    <row r="112" spans="1:10">
       <c r="A112" s="84" t="s">
         <v>210</v>
       </c>
@@ -5771,7 +5799,7 @@
       <c r="I112" s="87"/>
       <c r="J112" s="88"/>
     </row>
-    <row r="113" spans="1:10" hidden="1">
+    <row r="113" spans="1:10">
       <c r="A113" s="89" t="s">
         <v>220</v>
       </c>
@@ -5799,7 +5827,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1">
+    <row r="114" spans="1:10">
       <c r="A114" s="89" t="s">
         <v>220</v>
       </c>
@@ -5825,7 +5853,7 @@
       <c r="I114" s="92"/>
       <c r="J114" s="93"/>
     </row>
-    <row r="115" spans="1:10" hidden="1">
+    <row r="115" spans="1:10">
       <c r="A115" s="89" t="s">
         <v>220</v>
       </c>
@@ -5851,7 +5879,7 @@
       <c r="I115" s="92"/>
       <c r="J115" s="93"/>
     </row>
-    <row r="116" spans="1:10" hidden="1">
+    <row r="116" spans="1:10">
       <c r="A116" s="89" t="s">
         <v>220</v>
       </c>
@@ -5899,11 +5927,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J117" xr:uid="{F591B56F-9C16-43FE-9B5C-FD4AC86E6A15}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="プロト"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="6">
       <filters>
         <filter val="進行中"/>
@@ -5986,7 +6009,7 @@
       </c>
       <c r="B7" s="7">
         <f ca="1">MAX(0,B4-TODAY())</f>
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6011,7 +6034,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1D838DA-6C01-4DFD-980E-9C45A10CBCD9}">
-  <dimension ref="A2:B16"/>
+  <dimension ref="A2:B22"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:2">
@@ -6072,6 +6095,31 @@
     <row r="16" spans="1:2">
       <c r="B16" t="s">
         <v>254</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="B19" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="B20" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="B21" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="B22" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
